--- a/3.1.3 Planilla Casos de Prueba.xlsx
+++ b/3.1.3 Planilla Casos de Prueba.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\benja\Documents\BecasFind\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29199B7C-B7F5-4EB6-9790-B14A7FAFF56F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E724E9A-2DC3-441C-A354-25BA18A3F2C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="421">
   <si>
     <t>PLANILLA DE CASOS DE PRUEBA — BecasFind</t>
   </si>
@@ -1383,12 +1383,15 @@
   <si>
     <t>Redirigido a /explorar.</t>
   </si>
+  <si>
+    <t>x</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1397,27 +1400,49 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FF2F5496"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <i/>
       <sz val="9"/>
-      <color rgb="FF666666"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF2F5496"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FF666666"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -1470,26 +1495,42 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1794,7 +1835,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N71"/>
+  <dimension ref="A1:ED71"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1810,8 +1851,8 @@
     <col min="14" max="14" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:134" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="7"/>
@@ -1827,9 +1868,129 @@
       <c r="L1" s="7"/>
       <c r="M1" s="7"/>
       <c r="N1" s="7"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A2" s="6" t="s">
+      <c r="O1" s="8"/>
+      <c r="P1" s="8"/>
+      <c r="Q1" s="8"/>
+      <c r="R1" s="8"/>
+      <c r="S1" s="8"/>
+      <c r="T1" s="8"/>
+      <c r="U1" s="8"/>
+      <c r="V1" s="8"/>
+      <c r="W1" s="8"/>
+      <c r="X1" s="8"/>
+      <c r="Y1" s="8"/>
+      <c r="Z1" s="8"/>
+      <c r="AA1" s="8"/>
+      <c r="AB1" s="8"/>
+      <c r="AC1" s="8"/>
+      <c r="AD1" s="8"/>
+      <c r="AE1" s="8"/>
+      <c r="AF1" s="8"/>
+      <c r="AG1" s="8"/>
+      <c r="AH1" s="8"/>
+      <c r="AI1" s="8"/>
+      <c r="AJ1" s="8"/>
+      <c r="AK1" s="8"/>
+      <c r="AL1" s="8"/>
+      <c r="AM1" s="8"/>
+      <c r="AN1" s="8"/>
+      <c r="AO1" s="8"/>
+      <c r="AP1" s="8"/>
+      <c r="AQ1" s="8"/>
+      <c r="AR1" s="8"/>
+      <c r="AS1" s="8"/>
+      <c r="AT1" s="8"/>
+      <c r="AU1" s="8"/>
+      <c r="AV1" s="8"/>
+      <c r="AW1" s="8"/>
+      <c r="AX1" s="8"/>
+      <c r="AY1" s="8"/>
+      <c r="AZ1" s="8"/>
+      <c r="BA1" s="8"/>
+      <c r="BB1" s="8"/>
+      <c r="BC1" s="8"/>
+      <c r="BD1" s="8"/>
+      <c r="BE1" s="8"/>
+      <c r="BF1" s="8"/>
+      <c r="BG1" s="8"/>
+      <c r="BH1" s="8"/>
+      <c r="BI1" s="8"/>
+      <c r="BJ1" s="8"/>
+      <c r="BK1" s="8"/>
+      <c r="BL1" s="8"/>
+      <c r="BM1" s="8"/>
+      <c r="BN1" s="8"/>
+      <c r="BO1" s="8"/>
+      <c r="BP1" s="8"/>
+      <c r="BQ1" s="8"/>
+      <c r="BR1" s="8"/>
+      <c r="BS1" s="8"/>
+      <c r="BT1" s="8"/>
+      <c r="BU1" s="8"/>
+      <c r="BV1" s="8"/>
+      <c r="BW1" s="8"/>
+      <c r="BX1" s="8"/>
+      <c r="BY1" s="8"/>
+      <c r="BZ1" s="8"/>
+      <c r="CA1" s="8"/>
+      <c r="CB1" s="8"/>
+      <c r="CC1" s="8"/>
+      <c r="CD1" s="8"/>
+      <c r="CE1" s="8"/>
+      <c r="CF1" s="8"/>
+      <c r="CG1" s="8"/>
+      <c r="CH1" s="8"/>
+      <c r="CI1" s="8"/>
+      <c r="CJ1" s="8"/>
+      <c r="CK1" s="8"/>
+      <c r="CL1" s="8"/>
+      <c r="CM1" s="8"/>
+      <c r="CN1" s="8"/>
+      <c r="CO1" s="8"/>
+      <c r="CP1" s="8"/>
+      <c r="CQ1" s="8"/>
+      <c r="CR1" s="8"/>
+      <c r="CS1" s="8"/>
+      <c r="CT1" s="8"/>
+      <c r="CU1" s="8"/>
+      <c r="CV1" s="8"/>
+      <c r="CW1" s="8"/>
+      <c r="CX1" s="8"/>
+      <c r="CY1" s="8"/>
+      <c r="CZ1" s="8"/>
+      <c r="DA1" s="8"/>
+      <c r="DB1" s="8"/>
+      <c r="DC1" s="8"/>
+      <c r="DD1" s="8"/>
+      <c r="DE1" s="8"/>
+      <c r="DF1" s="8"/>
+      <c r="DG1" s="8"/>
+      <c r="DH1" s="8"/>
+      <c r="DI1" s="8"/>
+      <c r="DJ1" s="8"/>
+      <c r="DK1" s="8"/>
+      <c r="DL1" s="8"/>
+      <c r="DM1" s="8"/>
+      <c r="DN1" s="8"/>
+      <c r="DO1" s="8"/>
+      <c r="DP1" s="8"/>
+      <c r="DQ1" s="8"/>
+      <c r="DR1" s="8"/>
+      <c r="DS1" s="8"/>
+      <c r="DT1" s="8"/>
+      <c r="DU1" s="8"/>
+      <c r="DV1" s="8"/>
+      <c r="DW1" s="8"/>
+      <c r="DX1" s="8"/>
+      <c r="DY1" s="8"/>
+      <c r="DZ1" s="8"/>
+      <c r="EA1" s="8"/>
+      <c r="EB1" s="8"/>
+      <c r="EC1" s="8"/>
+      <c r="ED1" s="8"/>
+    </row>
+    <row r="2" spans="1:134" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="9" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="7"/>
@@ -1845,2328 +2006,4558 @@
       <c r="L2" s="7"/>
       <c r="M2" s="7"/>
       <c r="N2" s="7"/>
-    </row>
-    <row r="4" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
+      <c r="O2" s="8"/>
+      <c r="P2" s="8"/>
+      <c r="Q2" s="8"/>
+      <c r="R2" s="8"/>
+      <c r="S2" s="8"/>
+      <c r="T2" s="8"/>
+      <c r="U2" s="8"/>
+      <c r="V2" s="8"/>
+      <c r="W2" s="8"/>
+      <c r="X2" s="8"/>
+      <c r="Y2" s="8"/>
+      <c r="Z2" s="8"/>
+      <c r="AA2" s="8"/>
+      <c r="AB2" s="8"/>
+      <c r="AC2" s="8"/>
+      <c r="AD2" s="8"/>
+      <c r="AE2" s="8"/>
+      <c r="AF2" s="8"/>
+      <c r="AG2" s="8"/>
+      <c r="AH2" s="8"/>
+      <c r="AI2" s="8"/>
+      <c r="AJ2" s="8"/>
+      <c r="AK2" s="8"/>
+      <c r="AL2" s="8"/>
+      <c r="AM2" s="8"/>
+      <c r="AN2" s="8"/>
+      <c r="AO2" s="8"/>
+      <c r="AP2" s="8"/>
+      <c r="AQ2" s="8"/>
+      <c r="AR2" s="8"/>
+      <c r="AS2" s="8"/>
+      <c r="AT2" s="8"/>
+      <c r="AU2" s="8"/>
+      <c r="AV2" s="8"/>
+      <c r="AW2" s="8"/>
+      <c r="AX2" s="8"/>
+      <c r="AY2" s="8"/>
+      <c r="AZ2" s="8"/>
+      <c r="BA2" s="8"/>
+      <c r="BB2" s="8"/>
+      <c r="BC2" s="8"/>
+      <c r="BD2" s="8"/>
+      <c r="BE2" s="8"/>
+      <c r="BF2" s="8"/>
+      <c r="BG2" s="8"/>
+      <c r="BH2" s="8"/>
+      <c r="BI2" s="8"/>
+      <c r="BJ2" s="8"/>
+      <c r="BK2" s="8"/>
+      <c r="BL2" s="8"/>
+      <c r="BM2" s="8"/>
+      <c r="BN2" s="8"/>
+      <c r="BO2" s="8"/>
+      <c r="BP2" s="8"/>
+      <c r="BQ2" s="8"/>
+      <c r="BR2" s="8"/>
+      <c r="BS2" s="8"/>
+      <c r="BT2" s="8"/>
+      <c r="BU2" s="8"/>
+      <c r="BV2" s="8"/>
+      <c r="BW2" s="8"/>
+      <c r="BX2" s="8"/>
+      <c r="BY2" s="8"/>
+      <c r="BZ2" s="8"/>
+      <c r="CA2" s="8"/>
+      <c r="CB2" s="8"/>
+      <c r="CC2" s="8"/>
+      <c r="CD2" s="8"/>
+      <c r="CE2" s="8"/>
+      <c r="CF2" s="8"/>
+      <c r="CG2" s="8"/>
+      <c r="CH2" s="8"/>
+      <c r="CI2" s="8"/>
+      <c r="CJ2" s="8"/>
+      <c r="CK2" s="8"/>
+      <c r="CL2" s="8"/>
+      <c r="CM2" s="8"/>
+      <c r="CN2" s="8"/>
+      <c r="CO2" s="8"/>
+      <c r="CP2" s="8"/>
+      <c r="CQ2" s="8"/>
+      <c r="CR2" s="8"/>
+      <c r="CS2" s="8"/>
+      <c r="CT2" s="8"/>
+      <c r="CU2" s="8"/>
+      <c r="CV2" s="8"/>
+      <c r="CW2" s="8"/>
+      <c r="CX2" s="8"/>
+      <c r="CY2" s="8"/>
+      <c r="CZ2" s="8"/>
+      <c r="DA2" s="8"/>
+      <c r="DB2" s="8"/>
+      <c r="DC2" s="8"/>
+      <c r="DD2" s="8"/>
+      <c r="DE2" s="8"/>
+      <c r="DF2" s="8"/>
+      <c r="DG2" s="8"/>
+      <c r="DH2" s="8"/>
+      <c r="DI2" s="8"/>
+      <c r="DJ2" s="8"/>
+      <c r="DK2" s="8"/>
+      <c r="DL2" s="8"/>
+      <c r="DM2" s="8"/>
+      <c r="DN2" s="8"/>
+      <c r="DO2" s="8"/>
+      <c r="DP2" s="8"/>
+      <c r="DQ2" s="8"/>
+      <c r="DR2" s="8"/>
+      <c r="DS2" s="8"/>
+      <c r="DT2" s="8"/>
+      <c r="DU2" s="8"/>
+      <c r="DV2" s="8"/>
+      <c r="DW2" s="8"/>
+      <c r="DX2" s="8"/>
+      <c r="DY2" s="8"/>
+      <c r="DZ2" s="8"/>
+      <c r="EA2" s="8"/>
+      <c r="EB2" s="8"/>
+      <c r="EC2" s="8"/>
+      <c r="ED2" s="8"/>
+    </row>
+    <row r="3" spans="1:134" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="8"/>
+      <c r="O3" s="8"/>
+      <c r="P3" s="8"/>
+      <c r="Q3" s="8"/>
+      <c r="R3" s="8"/>
+      <c r="S3" s="8"/>
+      <c r="T3" s="8"/>
+      <c r="U3" s="8"/>
+      <c r="V3" s="8"/>
+      <c r="W3" s="8"/>
+      <c r="X3" s="8"/>
+      <c r="Y3" s="8"/>
+      <c r="Z3" s="8"/>
+      <c r="AA3" s="8"/>
+      <c r="AB3" s="8"/>
+      <c r="AC3" s="8"/>
+      <c r="AD3" s="8"/>
+      <c r="AE3" s="8"/>
+      <c r="AF3" s="8"/>
+      <c r="AG3" s="8"/>
+      <c r="AH3" s="8"/>
+      <c r="AI3" s="8"/>
+      <c r="AJ3" s="8"/>
+      <c r="AK3" s="8"/>
+      <c r="AL3" s="8"/>
+      <c r="AM3" s="8"/>
+      <c r="AN3" s="8"/>
+      <c r="AO3" s="8"/>
+      <c r="AP3" s="8"/>
+      <c r="AQ3" s="8"/>
+      <c r="AR3" s="8"/>
+      <c r="AS3" s="8"/>
+      <c r="AT3" s="8"/>
+      <c r="AU3" s="8"/>
+      <c r="AV3" s="8"/>
+      <c r="AW3" s="8"/>
+      <c r="AX3" s="8"/>
+      <c r="AY3" s="8"/>
+      <c r="AZ3" s="8"/>
+      <c r="BA3" s="8"/>
+      <c r="BB3" s="8"/>
+      <c r="BC3" s="8"/>
+      <c r="BD3" s="8"/>
+      <c r="BE3" s="8"/>
+      <c r="BF3" s="8"/>
+      <c r="BG3" s="8"/>
+      <c r="BH3" s="8"/>
+      <c r="BI3" s="8"/>
+      <c r="BJ3" s="8"/>
+      <c r="BK3" s="8"/>
+      <c r="BL3" s="8"/>
+      <c r="BM3" s="8"/>
+      <c r="BN3" s="8"/>
+      <c r="BO3" s="8"/>
+      <c r="BP3" s="8"/>
+      <c r="BQ3" s="8"/>
+      <c r="BR3" s="8"/>
+      <c r="BS3" s="8"/>
+      <c r="BT3" s="8"/>
+      <c r="BU3" s="8"/>
+      <c r="BV3" s="8"/>
+      <c r="BW3" s="8"/>
+      <c r="BX3" s="8"/>
+      <c r="BY3" s="8"/>
+      <c r="BZ3" s="8"/>
+      <c r="CA3" s="8"/>
+      <c r="CB3" s="8"/>
+      <c r="CC3" s="8"/>
+      <c r="CD3" s="8"/>
+      <c r="CE3" s="8"/>
+      <c r="CF3" s="8"/>
+      <c r="CG3" s="8"/>
+      <c r="CH3" s="8"/>
+      <c r="CI3" s="8"/>
+      <c r="CJ3" s="8"/>
+      <c r="CK3" s="8"/>
+      <c r="CL3" s="8"/>
+      <c r="CM3" s="8"/>
+      <c r="CN3" s="8"/>
+      <c r="CO3" s="8"/>
+      <c r="CP3" s="8"/>
+      <c r="CQ3" s="8"/>
+      <c r="CR3" s="8"/>
+      <c r="CS3" s="8"/>
+      <c r="CT3" s="8"/>
+      <c r="CU3" s="8"/>
+      <c r="CV3" s="8"/>
+      <c r="CW3" s="8"/>
+      <c r="CX3" s="8"/>
+      <c r="CY3" s="8"/>
+      <c r="CZ3" s="8"/>
+      <c r="DA3" s="8"/>
+      <c r="DB3" s="8"/>
+      <c r="DC3" s="8"/>
+      <c r="DD3" s="8"/>
+      <c r="DE3" s="8"/>
+      <c r="DF3" s="8"/>
+      <c r="DG3" s="8"/>
+      <c r="DH3" s="8"/>
+      <c r="DI3" s="8"/>
+      <c r="DJ3" s="8"/>
+      <c r="DK3" s="8"/>
+      <c r="DL3" s="8"/>
+      <c r="DM3" s="8"/>
+      <c r="DN3" s="8"/>
+      <c r="DO3" s="8"/>
+      <c r="DP3" s="8"/>
+      <c r="DQ3" s="8"/>
+      <c r="DR3" s="8"/>
+      <c r="DS3" s="8"/>
+      <c r="DT3" s="8"/>
+      <c r="DU3" s="8"/>
+      <c r="DV3" s="8"/>
+      <c r="DW3" s="8"/>
+      <c r="DX3" s="8"/>
+      <c r="DY3" s="8"/>
+      <c r="DZ3" s="8"/>
+      <c r="EA3" s="8"/>
+      <c r="EB3" s="8"/>
+      <c r="EC3" s="8"/>
+      <c r="ED3" s="8"/>
+    </row>
+    <row r="4" spans="1:134" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H4" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I4" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="J4" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="K4" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="L4" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="M4" s="1" t="s">
+      <c r="M4" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="N4" s="1" t="s">
+      <c r="N4" s="10" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="2">
+      <c r="O4" s="8"/>
+      <c r="P4" s="8"/>
+      <c r="Q4" s="8"/>
+      <c r="R4" s="8"/>
+      <c r="S4" s="8"/>
+      <c r="T4" s="8"/>
+      <c r="U4" s="8"/>
+      <c r="V4" s="8"/>
+      <c r="W4" s="8"/>
+      <c r="X4" s="8"/>
+      <c r="Y4" s="8"/>
+      <c r="Z4" s="8"/>
+      <c r="AA4" s="8"/>
+      <c r="AB4" s="8"/>
+      <c r="AC4" s="8"/>
+      <c r="AD4" s="8"/>
+      <c r="AE4" s="8"/>
+      <c r="AF4" s="8"/>
+      <c r="AG4" s="8"/>
+      <c r="AH4" s="8"/>
+      <c r="AI4" s="8"/>
+      <c r="AJ4" s="8"/>
+      <c r="AK4" s="8"/>
+      <c r="AL4" s="8"/>
+      <c r="AM4" s="8"/>
+      <c r="AN4" s="8"/>
+      <c r="AO4" s="8"/>
+      <c r="AP4" s="8"/>
+      <c r="AQ4" s="8"/>
+      <c r="AR4" s="8"/>
+      <c r="AS4" s="8"/>
+      <c r="AT4" s="8"/>
+      <c r="AU4" s="8"/>
+      <c r="AV4" s="8"/>
+      <c r="AW4" s="8"/>
+      <c r="AX4" s="8"/>
+      <c r="AY4" s="8"/>
+      <c r="AZ4" s="8"/>
+      <c r="BA4" s="8"/>
+      <c r="BB4" s="8"/>
+      <c r="BC4" s="8"/>
+      <c r="BD4" s="8"/>
+      <c r="BE4" s="8"/>
+      <c r="BF4" s="8"/>
+      <c r="BG4" s="8"/>
+      <c r="BH4" s="8"/>
+      <c r="BI4" s="8"/>
+      <c r="BJ4" s="8"/>
+      <c r="BK4" s="8"/>
+      <c r="BL4" s="8"/>
+      <c r="BM4" s="8"/>
+      <c r="BN4" s="8"/>
+      <c r="BO4" s="8"/>
+      <c r="BP4" s="8"/>
+      <c r="BQ4" s="8"/>
+      <c r="BR4" s="8"/>
+      <c r="BS4" s="8"/>
+      <c r="BT4" s="8"/>
+      <c r="BU4" s="8"/>
+      <c r="BV4" s="8"/>
+      <c r="BW4" s="8"/>
+      <c r="BX4" s="8"/>
+      <c r="BY4" s="8"/>
+      <c r="BZ4" s="8"/>
+      <c r="CA4" s="8"/>
+      <c r="CB4" s="8"/>
+      <c r="CC4" s="8"/>
+      <c r="CD4" s="8"/>
+      <c r="CE4" s="8"/>
+      <c r="CF4" s="8"/>
+      <c r="CG4" s="8"/>
+      <c r="CH4" s="8"/>
+      <c r="CI4" s="8"/>
+      <c r="CJ4" s="8"/>
+      <c r="CK4" s="8"/>
+      <c r="CL4" s="8"/>
+      <c r="CM4" s="8"/>
+      <c r="CN4" s="8"/>
+      <c r="CO4" s="8"/>
+      <c r="CP4" s="8"/>
+      <c r="CQ4" s="8"/>
+      <c r="CR4" s="8"/>
+      <c r="CS4" s="8"/>
+      <c r="CT4" s="8"/>
+      <c r="CU4" s="8"/>
+      <c r="CV4" s="8"/>
+      <c r="CW4" s="8"/>
+      <c r="CX4" s="8"/>
+      <c r="CY4" s="8"/>
+      <c r="CZ4" s="8"/>
+      <c r="DA4" s="8"/>
+      <c r="DB4" s="8"/>
+      <c r="DC4" s="8"/>
+      <c r="DD4" s="8"/>
+      <c r="DE4" s="8"/>
+      <c r="DF4" s="8"/>
+      <c r="DG4" s="8"/>
+      <c r="DH4" s="8"/>
+      <c r="DI4" s="8"/>
+      <c r="DJ4" s="8"/>
+      <c r="DK4" s="8"/>
+      <c r="DL4" s="8"/>
+      <c r="DM4" s="8"/>
+      <c r="DN4" s="8"/>
+      <c r="DO4" s="8"/>
+      <c r="DP4" s="8"/>
+      <c r="DQ4" s="8"/>
+      <c r="DR4" s="8"/>
+      <c r="DS4" s="8"/>
+      <c r="DT4" s="8"/>
+      <c r="DU4" s="8"/>
+      <c r="DV4" s="8"/>
+      <c r="DW4" s="8"/>
+      <c r="DX4" s="8"/>
+      <c r="DY4" s="8"/>
+      <c r="DZ4" s="8"/>
+      <c r="EA4" s="8"/>
+      <c r="EB4" s="8"/>
+      <c r="EC4" s="8"/>
+      <c r="ED4" s="8"/>
+    </row>
+    <row r="5" spans="1:134" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="11">
         <v>1</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="D5" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="I5" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3"/>
-    </row>
-    <row r="6" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="4">
+      <c r="J5" s="12" t="s">
+        <v>420</v>
+      </c>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="12"/>
+      <c r="N5" s="12"/>
+      <c r="O5" s="8"/>
+      <c r="P5" s="8"/>
+      <c r="Q5" s="8"/>
+      <c r="R5" s="8"/>
+      <c r="S5" s="8"/>
+      <c r="T5" s="8"/>
+      <c r="U5" s="8"/>
+      <c r="V5" s="8"/>
+      <c r="W5" s="8"/>
+      <c r="X5" s="8"/>
+      <c r="Y5" s="8"/>
+      <c r="Z5" s="8"/>
+      <c r="AA5" s="8"/>
+      <c r="AB5" s="8"/>
+      <c r="AC5" s="8"/>
+      <c r="AD5" s="8"/>
+      <c r="AE5" s="8"/>
+      <c r="AF5" s="8"/>
+      <c r="AG5" s="8"/>
+      <c r="AH5" s="8"/>
+      <c r="AI5" s="8"/>
+      <c r="AJ5" s="8"/>
+      <c r="AK5" s="8"/>
+      <c r="AL5" s="8"/>
+      <c r="AM5" s="8"/>
+      <c r="AN5" s="8"/>
+      <c r="AO5" s="8"/>
+      <c r="AP5" s="8"/>
+      <c r="AQ5" s="8"/>
+      <c r="AR5" s="8"/>
+      <c r="AS5" s="8"/>
+      <c r="AT5" s="8"/>
+      <c r="AU5" s="8"/>
+      <c r="AV5" s="8"/>
+      <c r="AW5" s="8"/>
+      <c r="AX5" s="8"/>
+      <c r="AY5" s="8"/>
+      <c r="AZ5" s="8"/>
+      <c r="BA5" s="8"/>
+      <c r="BB5" s="8"/>
+      <c r="BC5" s="8"/>
+      <c r="BD5" s="8"/>
+      <c r="BE5" s="8"/>
+      <c r="BF5" s="8"/>
+      <c r="BG5" s="8"/>
+      <c r="BH5" s="8"/>
+      <c r="BI5" s="8"/>
+      <c r="BJ5" s="8"/>
+      <c r="BK5" s="8"/>
+      <c r="BL5" s="8"/>
+      <c r="BM5" s="8"/>
+      <c r="BN5" s="8"/>
+      <c r="BO5" s="8"/>
+      <c r="BP5" s="8"/>
+      <c r="BQ5" s="8"/>
+      <c r="BR5" s="8"/>
+      <c r="BS5" s="8"/>
+      <c r="BT5" s="8"/>
+      <c r="BU5" s="8"/>
+      <c r="BV5" s="8"/>
+      <c r="BW5" s="8"/>
+      <c r="BX5" s="8"/>
+      <c r="BY5" s="8"/>
+      <c r="BZ5" s="8"/>
+      <c r="CA5" s="8"/>
+      <c r="CB5" s="8"/>
+      <c r="CC5" s="8"/>
+      <c r="CD5" s="8"/>
+      <c r="CE5" s="8"/>
+      <c r="CF5" s="8"/>
+      <c r="CG5" s="8"/>
+      <c r="CH5" s="8"/>
+      <c r="CI5" s="8"/>
+      <c r="CJ5" s="8"/>
+      <c r="CK5" s="8"/>
+      <c r="CL5" s="8"/>
+      <c r="CM5" s="8"/>
+      <c r="CN5" s="8"/>
+      <c r="CO5" s="8"/>
+      <c r="CP5" s="8"/>
+      <c r="CQ5" s="8"/>
+      <c r="CR5" s="8"/>
+      <c r="CS5" s="8"/>
+      <c r="CT5" s="8"/>
+      <c r="CU5" s="8"/>
+      <c r="CV5" s="8"/>
+      <c r="CW5" s="8"/>
+      <c r="CX5" s="8"/>
+      <c r="CY5" s="8"/>
+      <c r="CZ5" s="8"/>
+      <c r="DA5" s="8"/>
+      <c r="DB5" s="8"/>
+      <c r="DC5" s="8"/>
+      <c r="DD5" s="8"/>
+      <c r="DE5" s="8"/>
+      <c r="DF5" s="8"/>
+      <c r="DG5" s="8"/>
+      <c r="DH5" s="8"/>
+      <c r="DI5" s="8"/>
+      <c r="DJ5" s="8"/>
+      <c r="DK5" s="8"/>
+      <c r="DL5" s="8"/>
+      <c r="DM5" s="8"/>
+      <c r="DN5" s="8"/>
+      <c r="DO5" s="8"/>
+      <c r="DP5" s="8"/>
+      <c r="DQ5" s="8"/>
+      <c r="DR5" s="8"/>
+      <c r="DS5" s="8"/>
+      <c r="DT5" s="8"/>
+      <c r="DU5" s="8"/>
+      <c r="DV5" s="8"/>
+      <c r="DW5" s="8"/>
+      <c r="DX5" s="8"/>
+      <c r="DY5" s="8"/>
+      <c r="DZ5" s="8"/>
+      <c r="EA5" s="8"/>
+      <c r="EB5" s="8"/>
+      <c r="EC5" s="8"/>
+      <c r="ED5" s="8"/>
+    </row>
+    <row r="6" spans="1:134" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="13">
         <v>2</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="4" t="s">
+      <c r="D6" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="5"/>
-    </row>
-    <row r="7" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="2">
+      <c r="J6" s="14" t="s">
+        <v>420</v>
+      </c>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="14"/>
+      <c r="N6" s="14"/>
+      <c r="O6" s="8"/>
+      <c r="P6" s="8"/>
+      <c r="Q6" s="8"/>
+      <c r="R6" s="8"/>
+      <c r="S6" s="8"/>
+      <c r="T6" s="8"/>
+      <c r="U6" s="8"/>
+      <c r="V6" s="8"/>
+      <c r="W6" s="8"/>
+      <c r="X6" s="8"/>
+      <c r="Y6" s="8"/>
+      <c r="Z6" s="8"/>
+      <c r="AA6" s="8"/>
+      <c r="AB6" s="8"/>
+      <c r="AC6" s="8"/>
+      <c r="AD6" s="8"/>
+      <c r="AE6" s="8"/>
+      <c r="AF6" s="8"/>
+      <c r="AG6" s="8"/>
+      <c r="AH6" s="8"/>
+      <c r="AI6" s="8"/>
+      <c r="AJ6" s="8"/>
+      <c r="AK6" s="8"/>
+      <c r="AL6" s="8"/>
+      <c r="AM6" s="8"/>
+      <c r="AN6" s="8"/>
+      <c r="AO6" s="8"/>
+      <c r="AP6" s="8"/>
+      <c r="AQ6" s="8"/>
+      <c r="AR6" s="8"/>
+      <c r="AS6" s="8"/>
+      <c r="AT6" s="8"/>
+      <c r="AU6" s="8"/>
+      <c r="AV6" s="8"/>
+      <c r="AW6" s="8"/>
+      <c r="AX6" s="8"/>
+      <c r="AY6" s="8"/>
+      <c r="AZ6" s="8"/>
+      <c r="BA6" s="8"/>
+      <c r="BB6" s="8"/>
+      <c r="BC6" s="8"/>
+      <c r="BD6" s="8"/>
+      <c r="BE6" s="8"/>
+      <c r="BF6" s="8"/>
+      <c r="BG6" s="8"/>
+      <c r="BH6" s="8"/>
+      <c r="BI6" s="8"/>
+      <c r="BJ6" s="8"/>
+      <c r="BK6" s="8"/>
+      <c r="BL6" s="8"/>
+      <c r="BM6" s="8"/>
+      <c r="BN6" s="8"/>
+      <c r="BO6" s="8"/>
+      <c r="BP6" s="8"/>
+      <c r="BQ6" s="8"/>
+      <c r="BR6" s="8"/>
+      <c r="BS6" s="8"/>
+      <c r="BT6" s="8"/>
+      <c r="BU6" s="8"/>
+      <c r="BV6" s="8"/>
+      <c r="BW6" s="8"/>
+      <c r="BX6" s="8"/>
+      <c r="BY6" s="8"/>
+      <c r="BZ6" s="8"/>
+      <c r="CA6" s="8"/>
+      <c r="CB6" s="8"/>
+      <c r="CC6" s="8"/>
+      <c r="CD6" s="8"/>
+      <c r="CE6" s="8"/>
+      <c r="CF6" s="8"/>
+      <c r="CG6" s="8"/>
+      <c r="CH6" s="8"/>
+      <c r="CI6" s="8"/>
+      <c r="CJ6" s="8"/>
+      <c r="CK6" s="8"/>
+      <c r="CL6" s="8"/>
+      <c r="CM6" s="8"/>
+      <c r="CN6" s="8"/>
+      <c r="CO6" s="8"/>
+      <c r="CP6" s="8"/>
+      <c r="CQ6" s="8"/>
+      <c r="CR6" s="8"/>
+      <c r="CS6" s="8"/>
+      <c r="CT6" s="8"/>
+      <c r="CU6" s="8"/>
+      <c r="CV6" s="8"/>
+      <c r="CW6" s="8"/>
+      <c r="CX6" s="8"/>
+      <c r="CY6" s="8"/>
+      <c r="CZ6" s="8"/>
+      <c r="DA6" s="8"/>
+      <c r="DB6" s="8"/>
+      <c r="DC6" s="8"/>
+      <c r="DD6" s="8"/>
+      <c r="DE6" s="8"/>
+      <c r="DF6" s="8"/>
+      <c r="DG6" s="8"/>
+      <c r="DH6" s="8"/>
+      <c r="DI6" s="8"/>
+      <c r="DJ6" s="8"/>
+      <c r="DK6" s="8"/>
+      <c r="DL6" s="8"/>
+      <c r="DM6" s="8"/>
+      <c r="DN6" s="8"/>
+      <c r="DO6" s="8"/>
+      <c r="DP6" s="8"/>
+      <c r="DQ6" s="8"/>
+      <c r="DR6" s="8"/>
+      <c r="DS6" s="8"/>
+      <c r="DT6" s="8"/>
+      <c r="DU6" s="8"/>
+      <c r="DV6" s="8"/>
+      <c r="DW6" s="8"/>
+      <c r="DX6" s="8"/>
+      <c r="DY6" s="8"/>
+      <c r="DZ6" s="8"/>
+      <c r="EA6" s="8"/>
+      <c r="EB6" s="8"/>
+      <c r="EC6" s="8"/>
+      <c r="ED6" s="8"/>
+    </row>
+    <row r="7" spans="1:134" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="11">
         <v>3</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="D7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="H7" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="I7" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-      <c r="N7" s="3"/>
-    </row>
-    <row r="8" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="4">
+      <c r="J7" s="12" t="s">
+        <v>420</v>
+      </c>
+      <c r="K7" s="12"/>
+      <c r="L7" s="12"/>
+      <c r="M7" s="12"/>
+      <c r="N7" s="12"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
+      <c r="Q7" s="8"/>
+      <c r="R7" s="8"/>
+      <c r="S7" s="8"/>
+      <c r="T7" s="8"/>
+      <c r="U7" s="8"/>
+      <c r="V7" s="8"/>
+      <c r="W7" s="8"/>
+      <c r="X7" s="8"/>
+      <c r="Y7" s="8"/>
+      <c r="Z7" s="8"/>
+      <c r="AA7" s="8"/>
+      <c r="AB7" s="8"/>
+      <c r="AC7" s="8"/>
+      <c r="AD7" s="8"/>
+      <c r="AE7" s="8"/>
+      <c r="AF7" s="8"/>
+      <c r="AG7" s="8"/>
+      <c r="AH7" s="8"/>
+      <c r="AI7" s="8"/>
+      <c r="AJ7" s="8"/>
+      <c r="AK7" s="8"/>
+      <c r="AL7" s="8"/>
+      <c r="AM7" s="8"/>
+      <c r="AN7" s="8"/>
+      <c r="AO7" s="8"/>
+      <c r="AP7" s="8"/>
+      <c r="AQ7" s="8"/>
+      <c r="AR7" s="8"/>
+      <c r="AS7" s="8"/>
+      <c r="AT7" s="8"/>
+      <c r="AU7" s="8"/>
+      <c r="AV7" s="8"/>
+      <c r="AW7" s="8"/>
+      <c r="AX7" s="8"/>
+      <c r="AY7" s="8"/>
+      <c r="AZ7" s="8"/>
+      <c r="BA7" s="8"/>
+      <c r="BB7" s="8"/>
+      <c r="BC7" s="8"/>
+      <c r="BD7" s="8"/>
+      <c r="BE7" s="8"/>
+      <c r="BF7" s="8"/>
+      <c r="BG7" s="8"/>
+      <c r="BH7" s="8"/>
+      <c r="BI7" s="8"/>
+      <c r="BJ7" s="8"/>
+      <c r="BK7" s="8"/>
+      <c r="BL7" s="8"/>
+      <c r="BM7" s="8"/>
+      <c r="BN7" s="8"/>
+      <c r="BO7" s="8"/>
+      <c r="BP7" s="8"/>
+      <c r="BQ7" s="8"/>
+      <c r="BR7" s="8"/>
+      <c r="BS7" s="8"/>
+      <c r="BT7" s="8"/>
+      <c r="BU7" s="8"/>
+      <c r="BV7" s="8"/>
+      <c r="BW7" s="8"/>
+      <c r="BX7" s="8"/>
+      <c r="BY7" s="8"/>
+      <c r="BZ7" s="8"/>
+      <c r="CA7" s="8"/>
+      <c r="CB7" s="8"/>
+      <c r="CC7" s="8"/>
+      <c r="CD7" s="8"/>
+      <c r="CE7" s="8"/>
+      <c r="CF7" s="8"/>
+      <c r="CG7" s="8"/>
+      <c r="CH7" s="8"/>
+      <c r="CI7" s="8"/>
+      <c r="CJ7" s="8"/>
+      <c r="CK7" s="8"/>
+      <c r="CL7" s="8"/>
+      <c r="CM7" s="8"/>
+      <c r="CN7" s="8"/>
+      <c r="CO7" s="8"/>
+      <c r="CP7" s="8"/>
+      <c r="CQ7" s="8"/>
+      <c r="CR7" s="8"/>
+      <c r="CS7" s="8"/>
+      <c r="CT7" s="8"/>
+      <c r="CU7" s="8"/>
+      <c r="CV7" s="8"/>
+      <c r="CW7" s="8"/>
+      <c r="CX7" s="8"/>
+      <c r="CY7" s="8"/>
+      <c r="CZ7" s="8"/>
+      <c r="DA7" s="8"/>
+      <c r="DB7" s="8"/>
+      <c r="DC7" s="8"/>
+      <c r="DD7" s="8"/>
+      <c r="DE7" s="8"/>
+      <c r="DF7" s="8"/>
+      <c r="DG7" s="8"/>
+      <c r="DH7" s="8"/>
+      <c r="DI7" s="8"/>
+      <c r="DJ7" s="8"/>
+      <c r="DK7" s="8"/>
+      <c r="DL7" s="8"/>
+      <c r="DM7" s="8"/>
+      <c r="DN7" s="8"/>
+      <c r="DO7" s="8"/>
+      <c r="DP7" s="8"/>
+      <c r="DQ7" s="8"/>
+      <c r="DR7" s="8"/>
+      <c r="DS7" s="8"/>
+      <c r="DT7" s="8"/>
+      <c r="DU7" s="8"/>
+      <c r="DV7" s="8"/>
+      <c r="DW7" s="8"/>
+      <c r="DX7" s="8"/>
+      <c r="DY7" s="8"/>
+      <c r="DZ7" s="8"/>
+      <c r="EA7" s="8"/>
+      <c r="EB7" s="8"/>
+      <c r="EC7" s="8"/>
+      <c r="ED7" s="8"/>
+    </row>
+    <row r="8" spans="1:134" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="13">
         <v>4</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="4" t="s">
+      <c r="D8" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
-      <c r="N8" s="5"/>
-    </row>
-    <row r="9" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="2">
+      <c r="J8" s="14" t="s">
+        <v>420</v>
+      </c>
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="14"/>
+      <c r="N8" s="14"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
+      <c r="Q8" s="8"/>
+      <c r="R8" s="8"/>
+      <c r="S8" s="8"/>
+      <c r="T8" s="8"/>
+      <c r="U8" s="8"/>
+      <c r="V8" s="8"/>
+      <c r="W8" s="8"/>
+      <c r="X8" s="8"/>
+      <c r="Y8" s="8"/>
+      <c r="Z8" s="8"/>
+      <c r="AA8" s="8"/>
+      <c r="AB8" s="8"/>
+      <c r="AC8" s="8"/>
+      <c r="AD8" s="8"/>
+      <c r="AE8" s="8"/>
+      <c r="AF8" s="8"/>
+      <c r="AG8" s="8"/>
+      <c r="AH8" s="8"/>
+      <c r="AI8" s="8"/>
+      <c r="AJ8" s="8"/>
+      <c r="AK8" s="8"/>
+      <c r="AL8" s="8"/>
+      <c r="AM8" s="8"/>
+      <c r="AN8" s="8"/>
+      <c r="AO8" s="8"/>
+      <c r="AP8" s="8"/>
+      <c r="AQ8" s="8"/>
+      <c r="AR8" s="8"/>
+      <c r="AS8" s="8"/>
+      <c r="AT8" s="8"/>
+      <c r="AU8" s="8"/>
+      <c r="AV8" s="8"/>
+      <c r="AW8" s="8"/>
+      <c r="AX8" s="8"/>
+      <c r="AY8" s="8"/>
+      <c r="AZ8" s="8"/>
+      <c r="BA8" s="8"/>
+      <c r="BB8" s="8"/>
+      <c r="BC8" s="8"/>
+      <c r="BD8" s="8"/>
+      <c r="BE8" s="8"/>
+      <c r="BF8" s="8"/>
+      <c r="BG8" s="8"/>
+      <c r="BH8" s="8"/>
+      <c r="BI8" s="8"/>
+      <c r="BJ8" s="8"/>
+      <c r="BK8" s="8"/>
+      <c r="BL8" s="8"/>
+      <c r="BM8" s="8"/>
+      <c r="BN8" s="8"/>
+      <c r="BO8" s="8"/>
+      <c r="BP8" s="8"/>
+      <c r="BQ8" s="8"/>
+      <c r="BR8" s="8"/>
+      <c r="BS8" s="8"/>
+      <c r="BT8" s="8"/>
+      <c r="BU8" s="8"/>
+      <c r="BV8" s="8"/>
+      <c r="BW8" s="8"/>
+      <c r="BX8" s="8"/>
+      <c r="BY8" s="8"/>
+      <c r="BZ8" s="8"/>
+      <c r="CA8" s="8"/>
+      <c r="CB8" s="8"/>
+      <c r="CC8" s="8"/>
+      <c r="CD8" s="8"/>
+      <c r="CE8" s="8"/>
+      <c r="CF8" s="8"/>
+      <c r="CG8" s="8"/>
+      <c r="CH8" s="8"/>
+      <c r="CI8" s="8"/>
+      <c r="CJ8" s="8"/>
+      <c r="CK8" s="8"/>
+      <c r="CL8" s="8"/>
+      <c r="CM8" s="8"/>
+      <c r="CN8" s="8"/>
+      <c r="CO8" s="8"/>
+      <c r="CP8" s="8"/>
+      <c r="CQ8" s="8"/>
+      <c r="CR8" s="8"/>
+      <c r="CS8" s="8"/>
+      <c r="CT8" s="8"/>
+      <c r="CU8" s="8"/>
+      <c r="CV8" s="8"/>
+      <c r="CW8" s="8"/>
+      <c r="CX8" s="8"/>
+      <c r="CY8" s="8"/>
+      <c r="CZ8" s="8"/>
+      <c r="DA8" s="8"/>
+      <c r="DB8" s="8"/>
+      <c r="DC8" s="8"/>
+      <c r="DD8" s="8"/>
+      <c r="DE8" s="8"/>
+      <c r="DF8" s="8"/>
+      <c r="DG8" s="8"/>
+      <c r="DH8" s="8"/>
+      <c r="DI8" s="8"/>
+      <c r="DJ8" s="8"/>
+      <c r="DK8" s="8"/>
+      <c r="DL8" s="8"/>
+      <c r="DM8" s="8"/>
+      <c r="DN8" s="8"/>
+      <c r="DO8" s="8"/>
+      <c r="DP8" s="8"/>
+      <c r="DQ8" s="8"/>
+      <c r="DR8" s="8"/>
+      <c r="DS8" s="8"/>
+      <c r="DT8" s="8"/>
+      <c r="DU8" s="8"/>
+      <c r="DV8" s="8"/>
+      <c r="DW8" s="8"/>
+      <c r="DX8" s="8"/>
+      <c r="DY8" s="8"/>
+      <c r="DZ8" s="8"/>
+      <c r="EA8" s="8"/>
+      <c r="EB8" s="8"/>
+      <c r="EC8" s="8"/>
+      <c r="ED8" s="8"/>
+    </row>
+    <row r="9" spans="1:134" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="11">
         <v>5</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="D9" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="H9" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="I9" s="2" t="s">
+      <c r="I9" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3"/>
-    </row>
-    <row r="10" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="4">
+      <c r="J9" s="12" t="s">
+        <v>420</v>
+      </c>
+      <c r="K9" s="12"/>
+      <c r="L9" s="12"/>
+      <c r="M9" s="12"/>
+      <c r="N9" s="12"/>
+      <c r="O9" s="8"/>
+      <c r="P9" s="8"/>
+      <c r="Q9" s="8"/>
+      <c r="R9" s="8"/>
+      <c r="S9" s="8"/>
+      <c r="T9" s="8"/>
+      <c r="U9" s="8"/>
+      <c r="V9" s="8"/>
+      <c r="W9" s="8"/>
+      <c r="X9" s="8"/>
+      <c r="Y9" s="8"/>
+      <c r="Z9" s="8"/>
+      <c r="AA9" s="8"/>
+      <c r="AB9" s="8"/>
+      <c r="AC9" s="8"/>
+      <c r="AD9" s="8"/>
+      <c r="AE9" s="8"/>
+      <c r="AF9" s="8"/>
+      <c r="AG9" s="8"/>
+      <c r="AH9" s="8"/>
+      <c r="AI9" s="8"/>
+      <c r="AJ9" s="8"/>
+      <c r="AK9" s="8"/>
+      <c r="AL9" s="8"/>
+      <c r="AM9" s="8"/>
+      <c r="AN9" s="8"/>
+      <c r="AO9" s="8"/>
+      <c r="AP9" s="8"/>
+      <c r="AQ9" s="8"/>
+      <c r="AR9" s="8"/>
+      <c r="AS9" s="8"/>
+      <c r="AT9" s="8"/>
+      <c r="AU9" s="8"/>
+      <c r="AV9" s="8"/>
+      <c r="AW9" s="8"/>
+      <c r="AX9" s="8"/>
+      <c r="AY9" s="8"/>
+      <c r="AZ9" s="8"/>
+      <c r="BA9" s="8"/>
+      <c r="BB9" s="8"/>
+      <c r="BC9" s="8"/>
+      <c r="BD9" s="8"/>
+      <c r="BE9" s="8"/>
+      <c r="BF9" s="8"/>
+      <c r="BG9" s="8"/>
+      <c r="BH9" s="8"/>
+      <c r="BI9" s="8"/>
+      <c r="BJ9" s="8"/>
+      <c r="BK9" s="8"/>
+      <c r="BL9" s="8"/>
+      <c r="BM9" s="8"/>
+      <c r="BN9" s="8"/>
+      <c r="BO9" s="8"/>
+      <c r="BP9" s="8"/>
+      <c r="BQ9" s="8"/>
+      <c r="BR9" s="8"/>
+      <c r="BS9" s="8"/>
+      <c r="BT9" s="8"/>
+      <c r="BU9" s="8"/>
+      <c r="BV9" s="8"/>
+      <c r="BW9" s="8"/>
+      <c r="BX9" s="8"/>
+      <c r="BY9" s="8"/>
+      <c r="BZ9" s="8"/>
+      <c r="CA9" s="8"/>
+      <c r="CB9" s="8"/>
+      <c r="CC9" s="8"/>
+      <c r="CD9" s="8"/>
+      <c r="CE9" s="8"/>
+      <c r="CF9" s="8"/>
+      <c r="CG9" s="8"/>
+      <c r="CH9" s="8"/>
+      <c r="CI9" s="8"/>
+      <c r="CJ9" s="8"/>
+      <c r="CK9" s="8"/>
+      <c r="CL9" s="8"/>
+      <c r="CM9" s="8"/>
+      <c r="CN9" s="8"/>
+      <c r="CO9" s="8"/>
+      <c r="CP9" s="8"/>
+      <c r="CQ9" s="8"/>
+      <c r="CR9" s="8"/>
+      <c r="CS9" s="8"/>
+      <c r="CT9" s="8"/>
+      <c r="CU9" s="8"/>
+      <c r="CV9" s="8"/>
+      <c r="CW9" s="8"/>
+      <c r="CX9" s="8"/>
+      <c r="CY9" s="8"/>
+      <c r="CZ9" s="8"/>
+      <c r="DA9" s="8"/>
+      <c r="DB9" s="8"/>
+      <c r="DC9" s="8"/>
+      <c r="DD9" s="8"/>
+      <c r="DE9" s="8"/>
+      <c r="DF9" s="8"/>
+      <c r="DG9" s="8"/>
+      <c r="DH9" s="8"/>
+      <c r="DI9" s="8"/>
+      <c r="DJ9" s="8"/>
+      <c r="DK9" s="8"/>
+      <c r="DL9" s="8"/>
+      <c r="DM9" s="8"/>
+      <c r="DN9" s="8"/>
+      <c r="DO9" s="8"/>
+      <c r="DP9" s="8"/>
+      <c r="DQ9" s="8"/>
+      <c r="DR9" s="8"/>
+      <c r="DS9" s="8"/>
+      <c r="DT9" s="8"/>
+      <c r="DU9" s="8"/>
+      <c r="DV9" s="8"/>
+      <c r="DW9" s="8"/>
+      <c r="DX9" s="8"/>
+      <c r="DY9" s="8"/>
+      <c r="DZ9" s="8"/>
+      <c r="EA9" s="8"/>
+      <c r="EB9" s="8"/>
+      <c r="EC9" s="8"/>
+      <c r="ED9" s="8"/>
+    </row>
+    <row r="10" spans="1:134" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="13">
         <v>6</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" s="4" t="s">
+      <c r="D10" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="H10" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="I10" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5"/>
-      <c r="M10" s="5"/>
-      <c r="N10" s="5"/>
-    </row>
-    <row r="11" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="2">
+      <c r="J10" s="14" t="s">
+        <v>420</v>
+      </c>
+      <c r="K10" s="14"/>
+      <c r="L10" s="14"/>
+      <c r="M10" s="14"/>
+      <c r="N10" s="14"/>
+      <c r="O10" s="8"/>
+      <c r="P10" s="8"/>
+      <c r="Q10" s="8"/>
+      <c r="R10" s="8"/>
+      <c r="S10" s="8"/>
+      <c r="T10" s="8"/>
+      <c r="U10" s="8"/>
+      <c r="V10" s="8"/>
+      <c r="W10" s="8"/>
+      <c r="X10" s="8"/>
+      <c r="Y10" s="8"/>
+      <c r="Z10" s="8"/>
+      <c r="AA10" s="8"/>
+      <c r="AB10" s="8"/>
+      <c r="AC10" s="8"/>
+      <c r="AD10" s="8"/>
+      <c r="AE10" s="8"/>
+      <c r="AF10" s="8"/>
+      <c r="AG10" s="8"/>
+      <c r="AH10" s="8"/>
+      <c r="AI10" s="8"/>
+      <c r="AJ10" s="8"/>
+      <c r="AK10" s="8"/>
+      <c r="AL10" s="8"/>
+      <c r="AM10" s="8"/>
+      <c r="AN10" s="8"/>
+      <c r="AO10" s="8"/>
+      <c r="AP10" s="8"/>
+      <c r="AQ10" s="8"/>
+      <c r="AR10" s="8"/>
+      <c r="AS10" s="8"/>
+      <c r="AT10" s="8"/>
+      <c r="AU10" s="8"/>
+      <c r="AV10" s="8"/>
+      <c r="AW10" s="8"/>
+      <c r="AX10" s="8"/>
+      <c r="AY10" s="8"/>
+      <c r="AZ10" s="8"/>
+      <c r="BA10" s="8"/>
+      <c r="BB10" s="8"/>
+      <c r="BC10" s="8"/>
+      <c r="BD10" s="8"/>
+      <c r="BE10" s="8"/>
+      <c r="BF10" s="8"/>
+      <c r="BG10" s="8"/>
+      <c r="BH10" s="8"/>
+      <c r="BI10" s="8"/>
+      <c r="BJ10" s="8"/>
+      <c r="BK10" s="8"/>
+      <c r="BL10" s="8"/>
+      <c r="BM10" s="8"/>
+      <c r="BN10" s="8"/>
+      <c r="BO10" s="8"/>
+      <c r="BP10" s="8"/>
+      <c r="BQ10" s="8"/>
+      <c r="BR10" s="8"/>
+      <c r="BS10" s="8"/>
+      <c r="BT10" s="8"/>
+      <c r="BU10" s="8"/>
+      <c r="BV10" s="8"/>
+      <c r="BW10" s="8"/>
+      <c r="BX10" s="8"/>
+      <c r="BY10" s="8"/>
+      <c r="BZ10" s="8"/>
+      <c r="CA10" s="8"/>
+      <c r="CB10" s="8"/>
+      <c r="CC10" s="8"/>
+      <c r="CD10" s="8"/>
+      <c r="CE10" s="8"/>
+      <c r="CF10" s="8"/>
+      <c r="CG10" s="8"/>
+      <c r="CH10" s="8"/>
+      <c r="CI10" s="8"/>
+      <c r="CJ10" s="8"/>
+      <c r="CK10" s="8"/>
+      <c r="CL10" s="8"/>
+      <c r="CM10" s="8"/>
+      <c r="CN10" s="8"/>
+      <c r="CO10" s="8"/>
+      <c r="CP10" s="8"/>
+      <c r="CQ10" s="8"/>
+      <c r="CR10" s="8"/>
+      <c r="CS10" s="8"/>
+      <c r="CT10" s="8"/>
+      <c r="CU10" s="8"/>
+      <c r="CV10" s="8"/>
+      <c r="CW10" s="8"/>
+      <c r="CX10" s="8"/>
+      <c r="CY10" s="8"/>
+      <c r="CZ10" s="8"/>
+      <c r="DA10" s="8"/>
+      <c r="DB10" s="8"/>
+      <c r="DC10" s="8"/>
+      <c r="DD10" s="8"/>
+      <c r="DE10" s="8"/>
+      <c r="DF10" s="8"/>
+      <c r="DG10" s="8"/>
+      <c r="DH10" s="8"/>
+      <c r="DI10" s="8"/>
+      <c r="DJ10" s="8"/>
+      <c r="DK10" s="8"/>
+      <c r="DL10" s="8"/>
+      <c r="DM10" s="8"/>
+      <c r="DN10" s="8"/>
+      <c r="DO10" s="8"/>
+      <c r="DP10" s="8"/>
+      <c r="DQ10" s="8"/>
+      <c r="DR10" s="8"/>
+      <c r="DS10" s="8"/>
+      <c r="DT10" s="8"/>
+      <c r="DU10" s="8"/>
+      <c r="DV10" s="8"/>
+      <c r="DW10" s="8"/>
+      <c r="DX10" s="8"/>
+      <c r="DY10" s="8"/>
+      <c r="DZ10" s="8"/>
+      <c r="EA10" s="8"/>
+      <c r="EB10" s="8"/>
+      <c r="EC10" s="8"/>
+      <c r="ED10" s="8"/>
+    </row>
+    <row r="11" spans="1:134" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="11">
         <v>7</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="D11" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="G11" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="H11" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="I11" s="2" t="s">
+      <c r="I11" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="4">
+      <c r="J11" s="12" t="s">
+        <v>420</v>
+      </c>
+      <c r="K11" s="12"/>
+      <c r="L11" s="12"/>
+      <c r="M11" s="12"/>
+      <c r="N11" s="12"/>
+      <c r="O11" s="8"/>
+      <c r="P11" s="8"/>
+      <c r="Q11" s="8"/>
+      <c r="R11" s="8"/>
+      <c r="S11" s="8"/>
+      <c r="T11" s="8"/>
+      <c r="U11" s="8"/>
+      <c r="V11" s="8"/>
+      <c r="W11" s="8"/>
+      <c r="X11" s="8"/>
+      <c r="Y11" s="8"/>
+      <c r="Z11" s="8"/>
+      <c r="AA11" s="8"/>
+      <c r="AB11" s="8"/>
+      <c r="AC11" s="8"/>
+      <c r="AD11" s="8"/>
+      <c r="AE11" s="8"/>
+      <c r="AF11" s="8"/>
+      <c r="AG11" s="8"/>
+      <c r="AH11" s="8"/>
+      <c r="AI11" s="8"/>
+      <c r="AJ11" s="8"/>
+      <c r="AK11" s="8"/>
+      <c r="AL11" s="8"/>
+      <c r="AM11" s="8"/>
+      <c r="AN11" s="8"/>
+      <c r="AO11" s="8"/>
+      <c r="AP11" s="8"/>
+      <c r="AQ11" s="8"/>
+      <c r="AR11" s="8"/>
+      <c r="AS11" s="8"/>
+      <c r="AT11" s="8"/>
+      <c r="AU11" s="8"/>
+      <c r="AV11" s="8"/>
+      <c r="AW11" s="8"/>
+      <c r="AX11" s="8"/>
+      <c r="AY11" s="8"/>
+      <c r="AZ11" s="8"/>
+      <c r="BA11" s="8"/>
+      <c r="BB11" s="8"/>
+      <c r="BC11" s="8"/>
+      <c r="BD11" s="8"/>
+      <c r="BE11" s="8"/>
+      <c r="BF11" s="8"/>
+      <c r="BG11" s="8"/>
+      <c r="BH11" s="8"/>
+      <c r="BI11" s="8"/>
+      <c r="BJ11" s="8"/>
+      <c r="BK11" s="8"/>
+      <c r="BL11" s="8"/>
+      <c r="BM11" s="8"/>
+      <c r="BN11" s="8"/>
+      <c r="BO11" s="8"/>
+      <c r="BP11" s="8"/>
+      <c r="BQ11" s="8"/>
+      <c r="BR11" s="8"/>
+      <c r="BS11" s="8"/>
+      <c r="BT11" s="8"/>
+      <c r="BU11" s="8"/>
+      <c r="BV11" s="8"/>
+      <c r="BW11" s="8"/>
+      <c r="BX11" s="8"/>
+      <c r="BY11" s="8"/>
+      <c r="BZ11" s="8"/>
+      <c r="CA11" s="8"/>
+      <c r="CB11" s="8"/>
+      <c r="CC11" s="8"/>
+      <c r="CD11" s="8"/>
+      <c r="CE11" s="8"/>
+      <c r="CF11" s="8"/>
+      <c r="CG11" s="8"/>
+      <c r="CH11" s="8"/>
+      <c r="CI11" s="8"/>
+      <c r="CJ11" s="8"/>
+      <c r="CK11" s="8"/>
+      <c r="CL11" s="8"/>
+      <c r="CM11" s="8"/>
+      <c r="CN11" s="8"/>
+      <c r="CO11" s="8"/>
+      <c r="CP11" s="8"/>
+      <c r="CQ11" s="8"/>
+      <c r="CR11" s="8"/>
+      <c r="CS11" s="8"/>
+      <c r="CT11" s="8"/>
+      <c r="CU11" s="8"/>
+      <c r="CV11" s="8"/>
+      <c r="CW11" s="8"/>
+      <c r="CX11" s="8"/>
+      <c r="CY11" s="8"/>
+      <c r="CZ11" s="8"/>
+      <c r="DA11" s="8"/>
+      <c r="DB11" s="8"/>
+      <c r="DC11" s="8"/>
+      <c r="DD11" s="8"/>
+      <c r="DE11" s="8"/>
+      <c r="DF11" s="8"/>
+      <c r="DG11" s="8"/>
+      <c r="DH11" s="8"/>
+      <c r="DI11" s="8"/>
+      <c r="DJ11" s="8"/>
+      <c r="DK11" s="8"/>
+      <c r="DL11" s="8"/>
+      <c r="DM11" s="8"/>
+      <c r="DN11" s="8"/>
+      <c r="DO11" s="8"/>
+      <c r="DP11" s="8"/>
+      <c r="DQ11" s="8"/>
+      <c r="DR11" s="8"/>
+      <c r="DS11" s="8"/>
+      <c r="DT11" s="8"/>
+      <c r="DU11" s="8"/>
+      <c r="DV11" s="8"/>
+      <c r="DW11" s="8"/>
+      <c r="DX11" s="8"/>
+      <c r="DY11" s="8"/>
+      <c r="DZ11" s="8"/>
+      <c r="EA11" s="8"/>
+      <c r="EB11" s="8"/>
+      <c r="EC11" s="8"/>
+      <c r="ED11" s="8"/>
+    </row>
+    <row r="12" spans="1:134" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="13">
         <v>8</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D12" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E12" s="4" t="s">
+      <c r="D12" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="H12" s="4" t="s">
+      <c r="H12" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="I12" s="4" t="s">
+      <c r="I12" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
-      <c r="L12" s="5"/>
-      <c r="M12" s="5"/>
-      <c r="N12" s="5"/>
-    </row>
-    <row r="13" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="2">
+      <c r="J12" s="14" t="s">
+        <v>420</v>
+      </c>
+      <c r="K12" s="14"/>
+      <c r="L12" s="14"/>
+      <c r="M12" s="14"/>
+      <c r="N12" s="14"/>
+      <c r="O12" s="8"/>
+      <c r="P12" s="8"/>
+      <c r="Q12" s="8"/>
+      <c r="R12" s="8"/>
+      <c r="S12" s="8"/>
+      <c r="T12" s="8"/>
+      <c r="U12" s="8"/>
+      <c r="V12" s="8"/>
+      <c r="W12" s="8"/>
+      <c r="X12" s="8"/>
+      <c r="Y12" s="8"/>
+      <c r="Z12" s="8"/>
+      <c r="AA12" s="8"/>
+      <c r="AB12" s="8"/>
+      <c r="AC12" s="8"/>
+      <c r="AD12" s="8"/>
+      <c r="AE12" s="8"/>
+      <c r="AF12" s="8"/>
+      <c r="AG12" s="8"/>
+      <c r="AH12" s="8"/>
+      <c r="AI12" s="8"/>
+      <c r="AJ12" s="8"/>
+      <c r="AK12" s="8"/>
+      <c r="AL12" s="8"/>
+      <c r="AM12" s="8"/>
+      <c r="AN12" s="8"/>
+      <c r="AO12" s="8"/>
+      <c r="AP12" s="8"/>
+      <c r="AQ12" s="8"/>
+      <c r="AR12" s="8"/>
+      <c r="AS12" s="8"/>
+      <c r="AT12" s="8"/>
+      <c r="AU12" s="8"/>
+      <c r="AV12" s="8"/>
+      <c r="AW12" s="8"/>
+      <c r="AX12" s="8"/>
+      <c r="AY12" s="8"/>
+      <c r="AZ12" s="8"/>
+      <c r="BA12" s="8"/>
+      <c r="BB12" s="8"/>
+      <c r="BC12" s="8"/>
+      <c r="BD12" s="8"/>
+      <c r="BE12" s="8"/>
+      <c r="BF12" s="8"/>
+      <c r="BG12" s="8"/>
+      <c r="BH12" s="8"/>
+      <c r="BI12" s="8"/>
+      <c r="BJ12" s="8"/>
+      <c r="BK12" s="8"/>
+      <c r="BL12" s="8"/>
+      <c r="BM12" s="8"/>
+      <c r="BN12" s="8"/>
+      <c r="BO12" s="8"/>
+      <c r="BP12" s="8"/>
+      <c r="BQ12" s="8"/>
+      <c r="BR12" s="8"/>
+      <c r="BS12" s="8"/>
+      <c r="BT12" s="8"/>
+      <c r="BU12" s="8"/>
+      <c r="BV12" s="8"/>
+      <c r="BW12" s="8"/>
+      <c r="BX12" s="8"/>
+      <c r="BY12" s="8"/>
+      <c r="BZ12" s="8"/>
+      <c r="CA12" s="8"/>
+      <c r="CB12" s="8"/>
+      <c r="CC12" s="8"/>
+      <c r="CD12" s="8"/>
+      <c r="CE12" s="8"/>
+      <c r="CF12" s="8"/>
+      <c r="CG12" s="8"/>
+      <c r="CH12" s="8"/>
+      <c r="CI12" s="8"/>
+      <c r="CJ12" s="8"/>
+      <c r="CK12" s="8"/>
+      <c r="CL12" s="8"/>
+      <c r="CM12" s="8"/>
+      <c r="CN12" s="8"/>
+      <c r="CO12" s="8"/>
+      <c r="CP12" s="8"/>
+      <c r="CQ12" s="8"/>
+      <c r="CR12" s="8"/>
+      <c r="CS12" s="8"/>
+      <c r="CT12" s="8"/>
+      <c r="CU12" s="8"/>
+      <c r="CV12" s="8"/>
+      <c r="CW12" s="8"/>
+      <c r="CX12" s="8"/>
+      <c r="CY12" s="8"/>
+      <c r="CZ12" s="8"/>
+      <c r="DA12" s="8"/>
+      <c r="DB12" s="8"/>
+      <c r="DC12" s="8"/>
+      <c r="DD12" s="8"/>
+      <c r="DE12" s="8"/>
+      <c r="DF12" s="8"/>
+      <c r="DG12" s="8"/>
+      <c r="DH12" s="8"/>
+      <c r="DI12" s="8"/>
+      <c r="DJ12" s="8"/>
+      <c r="DK12" s="8"/>
+      <c r="DL12" s="8"/>
+      <c r="DM12" s="8"/>
+      <c r="DN12" s="8"/>
+      <c r="DO12" s="8"/>
+      <c r="DP12" s="8"/>
+      <c r="DQ12" s="8"/>
+      <c r="DR12" s="8"/>
+      <c r="DS12" s="8"/>
+      <c r="DT12" s="8"/>
+      <c r="DU12" s="8"/>
+      <c r="DV12" s="8"/>
+      <c r="DW12" s="8"/>
+      <c r="DX12" s="8"/>
+      <c r="DY12" s="8"/>
+      <c r="DZ12" s="8"/>
+      <c r="EA12" s="8"/>
+      <c r="EB12" s="8"/>
+      <c r="EC12" s="8"/>
+      <c r="ED12" s="8"/>
+    </row>
+    <row r="13" spans="1:134" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="11">
         <v>9</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="D13" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="F13" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="G13" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="H13" s="2" t="s">
+      <c r="H13" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="I13" s="2" t="s">
+      <c r="I13" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
-    </row>
-    <row r="14" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="4">
+      <c r="J13" s="12" t="s">
+        <v>420</v>
+      </c>
+      <c r="K13" s="12"/>
+      <c r="L13" s="12"/>
+      <c r="M13" s="12"/>
+      <c r="N13" s="12"/>
+      <c r="O13" s="8"/>
+      <c r="P13" s="8"/>
+      <c r="Q13" s="8"/>
+      <c r="R13" s="8"/>
+      <c r="S13" s="8"/>
+      <c r="T13" s="8"/>
+      <c r="U13" s="8"/>
+      <c r="V13" s="8"/>
+      <c r="W13" s="8"/>
+      <c r="X13" s="8"/>
+      <c r="Y13" s="8"/>
+      <c r="Z13" s="8"/>
+      <c r="AA13" s="8"/>
+      <c r="AB13" s="8"/>
+      <c r="AC13" s="8"/>
+      <c r="AD13" s="8"/>
+      <c r="AE13" s="8"/>
+      <c r="AF13" s="8"/>
+      <c r="AG13" s="8"/>
+      <c r="AH13" s="8"/>
+      <c r="AI13" s="8"/>
+      <c r="AJ13" s="8"/>
+      <c r="AK13" s="8"/>
+      <c r="AL13" s="8"/>
+      <c r="AM13" s="8"/>
+      <c r="AN13" s="8"/>
+      <c r="AO13" s="8"/>
+      <c r="AP13" s="8"/>
+      <c r="AQ13" s="8"/>
+      <c r="AR13" s="8"/>
+      <c r="AS13" s="8"/>
+      <c r="AT13" s="8"/>
+      <c r="AU13" s="8"/>
+      <c r="AV13" s="8"/>
+      <c r="AW13" s="8"/>
+      <c r="AX13" s="8"/>
+      <c r="AY13" s="8"/>
+      <c r="AZ13" s="8"/>
+      <c r="BA13" s="8"/>
+      <c r="BB13" s="8"/>
+      <c r="BC13" s="8"/>
+      <c r="BD13" s="8"/>
+      <c r="BE13" s="8"/>
+      <c r="BF13" s="8"/>
+      <c r="BG13" s="8"/>
+      <c r="BH13" s="8"/>
+      <c r="BI13" s="8"/>
+      <c r="BJ13" s="8"/>
+      <c r="BK13" s="8"/>
+      <c r="BL13" s="8"/>
+      <c r="BM13" s="8"/>
+      <c r="BN13" s="8"/>
+      <c r="BO13" s="8"/>
+      <c r="BP13" s="8"/>
+      <c r="BQ13" s="8"/>
+      <c r="BR13" s="8"/>
+      <c r="BS13" s="8"/>
+      <c r="BT13" s="8"/>
+      <c r="BU13" s="8"/>
+      <c r="BV13" s="8"/>
+      <c r="BW13" s="8"/>
+      <c r="BX13" s="8"/>
+      <c r="BY13" s="8"/>
+      <c r="BZ13" s="8"/>
+      <c r="CA13" s="8"/>
+      <c r="CB13" s="8"/>
+      <c r="CC13" s="8"/>
+      <c r="CD13" s="8"/>
+      <c r="CE13" s="8"/>
+      <c r="CF13" s="8"/>
+      <c r="CG13" s="8"/>
+      <c r="CH13" s="8"/>
+      <c r="CI13" s="8"/>
+      <c r="CJ13" s="8"/>
+      <c r="CK13" s="8"/>
+      <c r="CL13" s="8"/>
+      <c r="CM13" s="8"/>
+      <c r="CN13" s="8"/>
+      <c r="CO13" s="8"/>
+      <c r="CP13" s="8"/>
+      <c r="CQ13" s="8"/>
+      <c r="CR13" s="8"/>
+      <c r="CS13" s="8"/>
+      <c r="CT13" s="8"/>
+      <c r="CU13" s="8"/>
+      <c r="CV13" s="8"/>
+      <c r="CW13" s="8"/>
+      <c r="CX13" s="8"/>
+      <c r="CY13" s="8"/>
+      <c r="CZ13" s="8"/>
+      <c r="DA13" s="8"/>
+      <c r="DB13" s="8"/>
+      <c r="DC13" s="8"/>
+      <c r="DD13" s="8"/>
+      <c r="DE13" s="8"/>
+      <c r="DF13" s="8"/>
+      <c r="DG13" s="8"/>
+      <c r="DH13" s="8"/>
+      <c r="DI13" s="8"/>
+      <c r="DJ13" s="8"/>
+      <c r="DK13" s="8"/>
+      <c r="DL13" s="8"/>
+      <c r="DM13" s="8"/>
+      <c r="DN13" s="8"/>
+      <c r="DO13" s="8"/>
+      <c r="DP13" s="8"/>
+      <c r="DQ13" s="8"/>
+      <c r="DR13" s="8"/>
+      <c r="DS13" s="8"/>
+      <c r="DT13" s="8"/>
+      <c r="DU13" s="8"/>
+      <c r="DV13" s="8"/>
+      <c r="DW13" s="8"/>
+      <c r="DX13" s="8"/>
+      <c r="DY13" s="8"/>
+      <c r="DZ13" s="8"/>
+      <c r="EA13" s="8"/>
+      <c r="EB13" s="8"/>
+      <c r="EC13" s="8"/>
+      <c r="ED13" s="8"/>
+    </row>
+    <row r="14" spans="1:134" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="13">
         <v>10</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E14" s="4" t="s">
+      <c r="D14" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="H14" s="4" t="s">
+      <c r="H14" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="I14" s="4" t="s">
+      <c r="I14" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5"/>
-      <c r="M14" s="5"/>
-      <c r="N14" s="5"/>
-    </row>
-    <row r="15" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="2">
+      <c r="J14" s="14" t="s">
+        <v>420</v>
+      </c>
+      <c r="K14" s="14"/>
+      <c r="L14" s="14"/>
+      <c r="M14" s="14"/>
+      <c r="N14" s="14"/>
+      <c r="O14" s="8"/>
+      <c r="P14" s="8"/>
+      <c r="Q14" s="8"/>
+      <c r="R14" s="8"/>
+      <c r="S14" s="8"/>
+      <c r="T14" s="8"/>
+      <c r="U14" s="8"/>
+      <c r="V14" s="8"/>
+      <c r="W14" s="8"/>
+      <c r="X14" s="8"/>
+      <c r="Y14" s="8"/>
+      <c r="Z14" s="8"/>
+      <c r="AA14" s="8"/>
+      <c r="AB14" s="8"/>
+      <c r="AC14" s="8"/>
+      <c r="AD14" s="8"/>
+      <c r="AE14" s="8"/>
+      <c r="AF14" s="8"/>
+      <c r="AG14" s="8"/>
+      <c r="AH14" s="8"/>
+      <c r="AI14" s="8"/>
+      <c r="AJ14" s="8"/>
+      <c r="AK14" s="8"/>
+      <c r="AL14" s="8"/>
+      <c r="AM14" s="8"/>
+      <c r="AN14" s="8"/>
+      <c r="AO14" s="8"/>
+      <c r="AP14" s="8"/>
+      <c r="AQ14" s="8"/>
+      <c r="AR14" s="8"/>
+      <c r="AS14" s="8"/>
+      <c r="AT14" s="8"/>
+      <c r="AU14" s="8"/>
+      <c r="AV14" s="8"/>
+      <c r="AW14" s="8"/>
+      <c r="AX14" s="8"/>
+      <c r="AY14" s="8"/>
+      <c r="AZ14" s="8"/>
+      <c r="BA14" s="8"/>
+      <c r="BB14" s="8"/>
+      <c r="BC14" s="8"/>
+      <c r="BD14" s="8"/>
+      <c r="BE14" s="8"/>
+      <c r="BF14" s="8"/>
+      <c r="BG14" s="8"/>
+      <c r="BH14" s="8"/>
+      <c r="BI14" s="8"/>
+      <c r="BJ14" s="8"/>
+      <c r="BK14" s="8"/>
+      <c r="BL14" s="8"/>
+      <c r="BM14" s="8"/>
+      <c r="BN14" s="8"/>
+      <c r="BO14" s="8"/>
+      <c r="BP14" s="8"/>
+      <c r="BQ14" s="8"/>
+      <c r="BR14" s="8"/>
+      <c r="BS14" s="8"/>
+      <c r="BT14" s="8"/>
+      <c r="BU14" s="8"/>
+      <c r="BV14" s="8"/>
+      <c r="BW14" s="8"/>
+      <c r="BX14" s="8"/>
+      <c r="BY14" s="8"/>
+      <c r="BZ14" s="8"/>
+      <c r="CA14" s="8"/>
+      <c r="CB14" s="8"/>
+      <c r="CC14" s="8"/>
+      <c r="CD14" s="8"/>
+      <c r="CE14" s="8"/>
+      <c r="CF14" s="8"/>
+      <c r="CG14" s="8"/>
+      <c r="CH14" s="8"/>
+      <c r="CI14" s="8"/>
+      <c r="CJ14" s="8"/>
+      <c r="CK14" s="8"/>
+      <c r="CL14" s="8"/>
+      <c r="CM14" s="8"/>
+      <c r="CN14" s="8"/>
+      <c r="CO14" s="8"/>
+      <c r="CP14" s="8"/>
+      <c r="CQ14" s="8"/>
+      <c r="CR14" s="8"/>
+      <c r="CS14" s="8"/>
+      <c r="CT14" s="8"/>
+      <c r="CU14" s="8"/>
+      <c r="CV14" s="8"/>
+      <c r="CW14" s="8"/>
+      <c r="CX14" s="8"/>
+      <c r="CY14" s="8"/>
+      <c r="CZ14" s="8"/>
+      <c r="DA14" s="8"/>
+      <c r="DB14" s="8"/>
+      <c r="DC14" s="8"/>
+      <c r="DD14" s="8"/>
+      <c r="DE14" s="8"/>
+      <c r="DF14" s="8"/>
+      <c r="DG14" s="8"/>
+      <c r="DH14" s="8"/>
+      <c r="DI14" s="8"/>
+      <c r="DJ14" s="8"/>
+      <c r="DK14" s="8"/>
+      <c r="DL14" s="8"/>
+      <c r="DM14" s="8"/>
+      <c r="DN14" s="8"/>
+      <c r="DO14" s="8"/>
+      <c r="DP14" s="8"/>
+      <c r="DQ14" s="8"/>
+      <c r="DR14" s="8"/>
+      <c r="DS14" s="8"/>
+      <c r="DT14" s="8"/>
+      <c r="DU14" s="8"/>
+      <c r="DV14" s="8"/>
+      <c r="DW14" s="8"/>
+      <c r="DX14" s="8"/>
+      <c r="DY14" s="8"/>
+      <c r="DZ14" s="8"/>
+      <c r="EA14" s="8"/>
+      <c r="EB14" s="8"/>
+      <c r="EC14" s="8"/>
+      <c r="ED14" s="8"/>
+    </row>
+    <row r="15" spans="1:134" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="11">
         <v>11</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="D15" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="F15" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="G15" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="H15" s="2" t="s">
+      <c r="H15" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="I15" s="2" t="s">
+      <c r="I15" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
-      <c r="N15" s="3"/>
-    </row>
-    <row r="16" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="4">
+      <c r="J15" s="12" t="s">
+        <v>420</v>
+      </c>
+      <c r="K15" s="12"/>
+      <c r="L15" s="12"/>
+      <c r="M15" s="12"/>
+      <c r="N15" s="12"/>
+      <c r="O15" s="8"/>
+      <c r="P15" s="8"/>
+      <c r="Q15" s="8"/>
+      <c r="R15" s="8"/>
+      <c r="S15" s="8"/>
+      <c r="T15" s="8"/>
+      <c r="U15" s="8"/>
+      <c r="V15" s="8"/>
+      <c r="W15" s="8"/>
+      <c r="X15" s="8"/>
+      <c r="Y15" s="8"/>
+      <c r="Z15" s="8"/>
+      <c r="AA15" s="8"/>
+      <c r="AB15" s="8"/>
+      <c r="AC15" s="8"/>
+      <c r="AD15" s="8"/>
+      <c r="AE15" s="8"/>
+      <c r="AF15" s="8"/>
+      <c r="AG15" s="8"/>
+      <c r="AH15" s="8"/>
+      <c r="AI15" s="8"/>
+      <c r="AJ15" s="8"/>
+      <c r="AK15" s="8"/>
+      <c r="AL15" s="8"/>
+      <c r="AM15" s="8"/>
+      <c r="AN15" s="8"/>
+      <c r="AO15" s="8"/>
+      <c r="AP15" s="8"/>
+      <c r="AQ15" s="8"/>
+      <c r="AR15" s="8"/>
+      <c r="AS15" s="8"/>
+      <c r="AT15" s="8"/>
+      <c r="AU15" s="8"/>
+      <c r="AV15" s="8"/>
+      <c r="AW15" s="8"/>
+      <c r="AX15" s="8"/>
+      <c r="AY15" s="8"/>
+      <c r="AZ15" s="8"/>
+      <c r="BA15" s="8"/>
+      <c r="BB15" s="8"/>
+      <c r="BC15" s="8"/>
+      <c r="BD15" s="8"/>
+      <c r="BE15" s="8"/>
+      <c r="BF15" s="8"/>
+      <c r="BG15" s="8"/>
+      <c r="BH15" s="8"/>
+      <c r="BI15" s="8"/>
+      <c r="BJ15" s="8"/>
+      <c r="BK15" s="8"/>
+      <c r="BL15" s="8"/>
+      <c r="BM15" s="8"/>
+      <c r="BN15" s="8"/>
+      <c r="BO15" s="8"/>
+      <c r="BP15" s="8"/>
+      <c r="BQ15" s="8"/>
+      <c r="BR15" s="8"/>
+      <c r="BS15" s="8"/>
+      <c r="BT15" s="8"/>
+      <c r="BU15" s="8"/>
+      <c r="BV15" s="8"/>
+      <c r="BW15" s="8"/>
+      <c r="BX15" s="8"/>
+      <c r="BY15" s="8"/>
+      <c r="BZ15" s="8"/>
+      <c r="CA15" s="8"/>
+      <c r="CB15" s="8"/>
+      <c r="CC15" s="8"/>
+      <c r="CD15" s="8"/>
+      <c r="CE15" s="8"/>
+      <c r="CF15" s="8"/>
+      <c r="CG15" s="8"/>
+      <c r="CH15" s="8"/>
+      <c r="CI15" s="8"/>
+      <c r="CJ15" s="8"/>
+      <c r="CK15" s="8"/>
+      <c r="CL15" s="8"/>
+      <c r="CM15" s="8"/>
+      <c r="CN15" s="8"/>
+      <c r="CO15" s="8"/>
+      <c r="CP15" s="8"/>
+      <c r="CQ15" s="8"/>
+      <c r="CR15" s="8"/>
+      <c r="CS15" s="8"/>
+      <c r="CT15" s="8"/>
+      <c r="CU15" s="8"/>
+      <c r="CV15" s="8"/>
+      <c r="CW15" s="8"/>
+      <c r="CX15" s="8"/>
+      <c r="CY15" s="8"/>
+      <c r="CZ15" s="8"/>
+      <c r="DA15" s="8"/>
+      <c r="DB15" s="8"/>
+      <c r="DC15" s="8"/>
+      <c r="DD15" s="8"/>
+      <c r="DE15" s="8"/>
+      <c r="DF15" s="8"/>
+      <c r="DG15" s="8"/>
+      <c r="DH15" s="8"/>
+      <c r="DI15" s="8"/>
+      <c r="DJ15" s="8"/>
+      <c r="DK15" s="8"/>
+      <c r="DL15" s="8"/>
+      <c r="DM15" s="8"/>
+      <c r="DN15" s="8"/>
+      <c r="DO15" s="8"/>
+      <c r="DP15" s="8"/>
+      <c r="DQ15" s="8"/>
+      <c r="DR15" s="8"/>
+      <c r="DS15" s="8"/>
+      <c r="DT15" s="8"/>
+      <c r="DU15" s="8"/>
+      <c r="DV15" s="8"/>
+      <c r="DW15" s="8"/>
+      <c r="DX15" s="8"/>
+      <c r="DY15" s="8"/>
+      <c r="DZ15" s="8"/>
+      <c r="EA15" s="8"/>
+      <c r="EB15" s="8"/>
+      <c r="EC15" s="8"/>
+      <c r="ED15" s="8"/>
+    </row>
+    <row r="16" spans="1:134" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="13">
         <v>12</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="D16" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E16" s="4" t="s">
+      <c r="D16" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="H16" s="4" t="s">
+      <c r="H16" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="I16" s="4" t="s">
+      <c r="I16" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="J16" s="5"/>
-      <c r="K16" s="5"/>
-      <c r="L16" s="5"/>
-      <c r="M16" s="5"/>
-      <c r="N16" s="5"/>
-    </row>
-    <row r="17" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="2">
+      <c r="J16" s="14" t="s">
+        <v>420</v>
+      </c>
+      <c r="K16" s="14"/>
+      <c r="L16" s="14"/>
+      <c r="M16" s="14"/>
+      <c r="N16" s="14"/>
+      <c r="O16" s="8"/>
+      <c r="P16" s="8"/>
+      <c r="Q16" s="8"/>
+      <c r="R16" s="8"/>
+      <c r="S16" s="8"/>
+      <c r="T16" s="8"/>
+      <c r="U16" s="8"/>
+      <c r="V16" s="8"/>
+      <c r="W16" s="8"/>
+      <c r="X16" s="8"/>
+      <c r="Y16" s="8"/>
+      <c r="Z16" s="8"/>
+      <c r="AA16" s="8"/>
+      <c r="AB16" s="8"/>
+      <c r="AC16" s="8"/>
+      <c r="AD16" s="8"/>
+      <c r="AE16" s="8"/>
+      <c r="AF16" s="8"/>
+      <c r="AG16" s="8"/>
+      <c r="AH16" s="8"/>
+      <c r="AI16" s="8"/>
+      <c r="AJ16" s="8"/>
+      <c r="AK16" s="8"/>
+      <c r="AL16" s="8"/>
+      <c r="AM16" s="8"/>
+      <c r="AN16" s="8"/>
+      <c r="AO16" s="8"/>
+      <c r="AP16" s="8"/>
+      <c r="AQ16" s="8"/>
+      <c r="AR16" s="8"/>
+      <c r="AS16" s="8"/>
+      <c r="AT16" s="8"/>
+      <c r="AU16" s="8"/>
+      <c r="AV16" s="8"/>
+      <c r="AW16" s="8"/>
+      <c r="AX16" s="8"/>
+      <c r="AY16" s="8"/>
+      <c r="AZ16" s="8"/>
+      <c r="BA16" s="8"/>
+      <c r="BB16" s="8"/>
+      <c r="BC16" s="8"/>
+      <c r="BD16" s="8"/>
+      <c r="BE16" s="8"/>
+      <c r="BF16" s="8"/>
+      <c r="BG16" s="8"/>
+      <c r="BH16" s="8"/>
+      <c r="BI16" s="8"/>
+      <c r="BJ16" s="8"/>
+      <c r="BK16" s="8"/>
+      <c r="BL16" s="8"/>
+      <c r="BM16" s="8"/>
+      <c r="BN16" s="8"/>
+      <c r="BO16" s="8"/>
+      <c r="BP16" s="8"/>
+      <c r="BQ16" s="8"/>
+      <c r="BR16" s="8"/>
+      <c r="BS16" s="8"/>
+      <c r="BT16" s="8"/>
+      <c r="BU16" s="8"/>
+      <c r="BV16" s="8"/>
+      <c r="BW16" s="8"/>
+      <c r="BX16" s="8"/>
+      <c r="BY16" s="8"/>
+      <c r="BZ16" s="8"/>
+      <c r="CA16" s="8"/>
+      <c r="CB16" s="8"/>
+      <c r="CC16" s="8"/>
+      <c r="CD16" s="8"/>
+      <c r="CE16" s="8"/>
+      <c r="CF16" s="8"/>
+      <c r="CG16" s="8"/>
+      <c r="CH16" s="8"/>
+      <c r="CI16" s="8"/>
+      <c r="CJ16" s="8"/>
+      <c r="CK16" s="8"/>
+      <c r="CL16" s="8"/>
+      <c r="CM16" s="8"/>
+      <c r="CN16" s="8"/>
+      <c r="CO16" s="8"/>
+      <c r="CP16" s="8"/>
+      <c r="CQ16" s="8"/>
+      <c r="CR16" s="8"/>
+      <c r="CS16" s="8"/>
+      <c r="CT16" s="8"/>
+      <c r="CU16" s="8"/>
+      <c r="CV16" s="8"/>
+      <c r="CW16" s="8"/>
+      <c r="CX16" s="8"/>
+      <c r="CY16" s="8"/>
+      <c r="CZ16" s="8"/>
+      <c r="DA16" s="8"/>
+      <c r="DB16" s="8"/>
+      <c r="DC16" s="8"/>
+      <c r="DD16" s="8"/>
+      <c r="DE16" s="8"/>
+      <c r="DF16" s="8"/>
+      <c r="DG16" s="8"/>
+      <c r="DH16" s="8"/>
+      <c r="DI16" s="8"/>
+      <c r="DJ16" s="8"/>
+      <c r="DK16" s="8"/>
+      <c r="DL16" s="8"/>
+      <c r="DM16" s="8"/>
+      <c r="DN16" s="8"/>
+      <c r="DO16" s="8"/>
+      <c r="DP16" s="8"/>
+      <c r="DQ16" s="8"/>
+      <c r="DR16" s="8"/>
+      <c r="DS16" s="8"/>
+      <c r="DT16" s="8"/>
+      <c r="DU16" s="8"/>
+      <c r="DV16" s="8"/>
+      <c r="DW16" s="8"/>
+      <c r="DX16" s="8"/>
+      <c r="DY16" s="8"/>
+      <c r="DZ16" s="8"/>
+      <c r="EA16" s="8"/>
+      <c r="EB16" s="8"/>
+      <c r="EC16" s="8"/>
+      <c r="ED16" s="8"/>
+    </row>
+    <row r="17" spans="1:134" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="11">
         <v>13</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="D17" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="F17" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="G17" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="H17" s="2" t="s">
+      <c r="H17" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="I17" s="2" t="s">
+      <c r="I17" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
-      <c r="M17" s="3"/>
-      <c r="N17" s="3"/>
-    </row>
-    <row r="18" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="4">
+      <c r="J17" s="12" t="s">
+        <v>420</v>
+      </c>
+      <c r="K17" s="12"/>
+      <c r="L17" s="12"/>
+      <c r="M17" s="12"/>
+      <c r="N17" s="12"/>
+      <c r="O17" s="8"/>
+      <c r="P17" s="8"/>
+      <c r="Q17" s="8"/>
+      <c r="R17" s="8"/>
+      <c r="S17" s="8"/>
+      <c r="T17" s="8"/>
+      <c r="U17" s="8"/>
+      <c r="V17" s="8"/>
+      <c r="W17" s="8"/>
+      <c r="X17" s="8"/>
+      <c r="Y17" s="8"/>
+      <c r="Z17" s="8"/>
+      <c r="AA17" s="8"/>
+      <c r="AB17" s="8"/>
+      <c r="AC17" s="8"/>
+      <c r="AD17" s="8"/>
+      <c r="AE17" s="8"/>
+      <c r="AF17" s="8"/>
+      <c r="AG17" s="8"/>
+      <c r="AH17" s="8"/>
+      <c r="AI17" s="8"/>
+      <c r="AJ17" s="8"/>
+      <c r="AK17" s="8"/>
+      <c r="AL17" s="8"/>
+      <c r="AM17" s="8"/>
+      <c r="AN17" s="8"/>
+      <c r="AO17" s="8"/>
+      <c r="AP17" s="8"/>
+      <c r="AQ17" s="8"/>
+      <c r="AR17" s="8"/>
+      <c r="AS17" s="8"/>
+      <c r="AT17" s="8"/>
+      <c r="AU17" s="8"/>
+      <c r="AV17" s="8"/>
+      <c r="AW17" s="8"/>
+      <c r="AX17" s="8"/>
+      <c r="AY17" s="8"/>
+      <c r="AZ17" s="8"/>
+      <c r="BA17" s="8"/>
+      <c r="BB17" s="8"/>
+      <c r="BC17" s="8"/>
+      <c r="BD17" s="8"/>
+      <c r="BE17" s="8"/>
+      <c r="BF17" s="8"/>
+      <c r="BG17" s="8"/>
+      <c r="BH17" s="8"/>
+      <c r="BI17" s="8"/>
+      <c r="BJ17" s="8"/>
+      <c r="BK17" s="8"/>
+      <c r="BL17" s="8"/>
+      <c r="BM17" s="8"/>
+      <c r="BN17" s="8"/>
+      <c r="BO17" s="8"/>
+      <c r="BP17" s="8"/>
+      <c r="BQ17" s="8"/>
+      <c r="BR17" s="8"/>
+      <c r="BS17" s="8"/>
+      <c r="BT17" s="8"/>
+      <c r="BU17" s="8"/>
+      <c r="BV17" s="8"/>
+      <c r="BW17" s="8"/>
+      <c r="BX17" s="8"/>
+      <c r="BY17" s="8"/>
+      <c r="BZ17" s="8"/>
+      <c r="CA17" s="8"/>
+      <c r="CB17" s="8"/>
+      <c r="CC17" s="8"/>
+      <c r="CD17" s="8"/>
+      <c r="CE17" s="8"/>
+      <c r="CF17" s="8"/>
+      <c r="CG17" s="8"/>
+      <c r="CH17" s="8"/>
+      <c r="CI17" s="8"/>
+      <c r="CJ17" s="8"/>
+      <c r="CK17" s="8"/>
+      <c r="CL17" s="8"/>
+      <c r="CM17" s="8"/>
+      <c r="CN17" s="8"/>
+      <c r="CO17" s="8"/>
+      <c r="CP17" s="8"/>
+      <c r="CQ17" s="8"/>
+      <c r="CR17" s="8"/>
+      <c r="CS17" s="8"/>
+      <c r="CT17" s="8"/>
+      <c r="CU17" s="8"/>
+      <c r="CV17" s="8"/>
+      <c r="CW17" s="8"/>
+      <c r="CX17" s="8"/>
+      <c r="CY17" s="8"/>
+      <c r="CZ17" s="8"/>
+      <c r="DA17" s="8"/>
+      <c r="DB17" s="8"/>
+      <c r="DC17" s="8"/>
+      <c r="DD17" s="8"/>
+      <c r="DE17" s="8"/>
+      <c r="DF17" s="8"/>
+      <c r="DG17" s="8"/>
+      <c r="DH17" s="8"/>
+      <c r="DI17" s="8"/>
+      <c r="DJ17" s="8"/>
+      <c r="DK17" s="8"/>
+      <c r="DL17" s="8"/>
+      <c r="DM17" s="8"/>
+      <c r="DN17" s="8"/>
+      <c r="DO17" s="8"/>
+      <c r="DP17" s="8"/>
+      <c r="DQ17" s="8"/>
+      <c r="DR17" s="8"/>
+      <c r="DS17" s="8"/>
+      <c r="DT17" s="8"/>
+      <c r="DU17" s="8"/>
+      <c r="DV17" s="8"/>
+      <c r="DW17" s="8"/>
+      <c r="DX17" s="8"/>
+      <c r="DY17" s="8"/>
+      <c r="DZ17" s="8"/>
+      <c r="EA17" s="8"/>
+      <c r="EB17" s="8"/>
+      <c r="EC17" s="8"/>
+      <c r="ED17" s="8"/>
+    </row>
+    <row r="18" spans="1:134" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="13">
         <v>14</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="D18" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E18" s="4" t="s">
+      <c r="D18" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="F18" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="G18" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="H18" s="4" t="s">
+      <c r="H18" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="I18" s="4" t="s">
+      <c r="I18" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="J18" s="5"/>
-      <c r="K18" s="5"/>
-      <c r="L18" s="5"/>
-      <c r="M18" s="5"/>
-      <c r="N18" s="5"/>
-    </row>
-    <row r="19" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="2">
+      <c r="J18" s="14" t="s">
+        <v>420</v>
+      </c>
+      <c r="K18" s="14"/>
+      <c r="L18" s="14"/>
+      <c r="M18" s="14"/>
+      <c r="N18" s="14"/>
+      <c r="O18" s="8"/>
+      <c r="P18" s="8"/>
+      <c r="Q18" s="8"/>
+      <c r="R18" s="8"/>
+      <c r="S18" s="8"/>
+      <c r="T18" s="8"/>
+      <c r="U18" s="8"/>
+      <c r="V18" s="8"/>
+      <c r="W18" s="8"/>
+      <c r="X18" s="8"/>
+      <c r="Y18" s="8"/>
+      <c r="Z18" s="8"/>
+      <c r="AA18" s="8"/>
+      <c r="AB18" s="8"/>
+      <c r="AC18" s="8"/>
+      <c r="AD18" s="8"/>
+      <c r="AE18" s="8"/>
+      <c r="AF18" s="8"/>
+      <c r="AG18" s="8"/>
+      <c r="AH18" s="8"/>
+      <c r="AI18" s="8"/>
+      <c r="AJ18" s="8"/>
+      <c r="AK18" s="8"/>
+      <c r="AL18" s="8"/>
+      <c r="AM18" s="8"/>
+      <c r="AN18" s="8"/>
+      <c r="AO18" s="8"/>
+      <c r="AP18" s="8"/>
+      <c r="AQ18" s="8"/>
+      <c r="AR18" s="8"/>
+      <c r="AS18" s="8"/>
+      <c r="AT18" s="8"/>
+      <c r="AU18" s="8"/>
+      <c r="AV18" s="8"/>
+      <c r="AW18" s="8"/>
+      <c r="AX18" s="8"/>
+      <c r="AY18" s="8"/>
+      <c r="AZ18" s="8"/>
+      <c r="BA18" s="8"/>
+      <c r="BB18" s="8"/>
+      <c r="BC18" s="8"/>
+      <c r="BD18" s="8"/>
+      <c r="BE18" s="8"/>
+      <c r="BF18" s="8"/>
+      <c r="BG18" s="8"/>
+      <c r="BH18" s="8"/>
+      <c r="BI18" s="8"/>
+      <c r="BJ18" s="8"/>
+      <c r="BK18" s="8"/>
+      <c r="BL18" s="8"/>
+      <c r="BM18" s="8"/>
+      <c r="BN18" s="8"/>
+      <c r="BO18" s="8"/>
+      <c r="BP18" s="8"/>
+      <c r="BQ18" s="8"/>
+      <c r="BR18" s="8"/>
+      <c r="BS18" s="8"/>
+      <c r="BT18" s="8"/>
+      <c r="BU18" s="8"/>
+      <c r="BV18" s="8"/>
+      <c r="BW18" s="8"/>
+      <c r="BX18" s="8"/>
+      <c r="BY18" s="8"/>
+      <c r="BZ18" s="8"/>
+      <c r="CA18" s="8"/>
+      <c r="CB18" s="8"/>
+      <c r="CC18" s="8"/>
+      <c r="CD18" s="8"/>
+      <c r="CE18" s="8"/>
+      <c r="CF18" s="8"/>
+      <c r="CG18" s="8"/>
+      <c r="CH18" s="8"/>
+      <c r="CI18" s="8"/>
+      <c r="CJ18" s="8"/>
+      <c r="CK18" s="8"/>
+      <c r="CL18" s="8"/>
+      <c r="CM18" s="8"/>
+      <c r="CN18" s="8"/>
+      <c r="CO18" s="8"/>
+      <c r="CP18" s="8"/>
+      <c r="CQ18" s="8"/>
+      <c r="CR18" s="8"/>
+      <c r="CS18" s="8"/>
+      <c r="CT18" s="8"/>
+      <c r="CU18" s="8"/>
+      <c r="CV18" s="8"/>
+      <c r="CW18" s="8"/>
+      <c r="CX18" s="8"/>
+      <c r="CY18" s="8"/>
+      <c r="CZ18" s="8"/>
+      <c r="DA18" s="8"/>
+      <c r="DB18" s="8"/>
+      <c r="DC18" s="8"/>
+      <c r="DD18" s="8"/>
+      <c r="DE18" s="8"/>
+      <c r="DF18" s="8"/>
+      <c r="DG18" s="8"/>
+      <c r="DH18" s="8"/>
+      <c r="DI18" s="8"/>
+      <c r="DJ18" s="8"/>
+      <c r="DK18" s="8"/>
+      <c r="DL18" s="8"/>
+      <c r="DM18" s="8"/>
+      <c r="DN18" s="8"/>
+      <c r="DO18" s="8"/>
+      <c r="DP18" s="8"/>
+      <c r="DQ18" s="8"/>
+      <c r="DR18" s="8"/>
+      <c r="DS18" s="8"/>
+      <c r="DT18" s="8"/>
+      <c r="DU18" s="8"/>
+      <c r="DV18" s="8"/>
+      <c r="DW18" s="8"/>
+      <c r="DX18" s="8"/>
+      <c r="DY18" s="8"/>
+      <c r="DZ18" s="8"/>
+      <c r="EA18" s="8"/>
+      <c r="EB18" s="8"/>
+      <c r="EC18" s="8"/>
+      <c r="ED18" s="8"/>
+    </row>
+    <row r="19" spans="1:134" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="11">
         <v>15</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="D19" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="F19" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="G19" s="2" t="s">
+      <c r="G19" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="H19" s="2" t="s">
+      <c r="H19" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="I19" s="2" t="s">
+      <c r="I19" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
-      <c r="L19" s="3"/>
-      <c r="M19" s="3"/>
-      <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="4">
+      <c r="J19" s="12" t="s">
+        <v>420</v>
+      </c>
+      <c r="K19" s="12"/>
+      <c r="L19" s="12"/>
+      <c r="M19" s="12"/>
+      <c r="N19" s="12"/>
+      <c r="O19" s="8"/>
+      <c r="P19" s="8"/>
+      <c r="Q19" s="8"/>
+      <c r="R19" s="8"/>
+      <c r="S19" s="8"/>
+      <c r="T19" s="8"/>
+      <c r="U19" s="8"/>
+      <c r="V19" s="8"/>
+      <c r="W19" s="8"/>
+      <c r="X19" s="8"/>
+      <c r="Y19" s="8"/>
+      <c r="Z19" s="8"/>
+      <c r="AA19" s="8"/>
+      <c r="AB19" s="8"/>
+      <c r="AC19" s="8"/>
+      <c r="AD19" s="8"/>
+      <c r="AE19" s="8"/>
+      <c r="AF19" s="8"/>
+      <c r="AG19" s="8"/>
+      <c r="AH19" s="8"/>
+      <c r="AI19" s="8"/>
+      <c r="AJ19" s="8"/>
+      <c r="AK19" s="8"/>
+      <c r="AL19" s="8"/>
+      <c r="AM19" s="8"/>
+      <c r="AN19" s="8"/>
+      <c r="AO19" s="8"/>
+      <c r="AP19" s="8"/>
+      <c r="AQ19" s="8"/>
+      <c r="AR19" s="8"/>
+      <c r="AS19" s="8"/>
+      <c r="AT19" s="8"/>
+      <c r="AU19" s="8"/>
+      <c r="AV19" s="8"/>
+      <c r="AW19" s="8"/>
+      <c r="AX19" s="8"/>
+      <c r="AY19" s="8"/>
+      <c r="AZ19" s="8"/>
+      <c r="BA19" s="8"/>
+      <c r="BB19" s="8"/>
+      <c r="BC19" s="8"/>
+      <c r="BD19" s="8"/>
+      <c r="BE19" s="8"/>
+      <c r="BF19" s="8"/>
+      <c r="BG19" s="8"/>
+      <c r="BH19" s="8"/>
+      <c r="BI19" s="8"/>
+      <c r="BJ19" s="8"/>
+      <c r="BK19" s="8"/>
+      <c r="BL19" s="8"/>
+      <c r="BM19" s="8"/>
+      <c r="BN19" s="8"/>
+      <c r="BO19" s="8"/>
+      <c r="BP19" s="8"/>
+      <c r="BQ19" s="8"/>
+      <c r="BR19" s="8"/>
+      <c r="BS19" s="8"/>
+      <c r="BT19" s="8"/>
+      <c r="BU19" s="8"/>
+      <c r="BV19" s="8"/>
+      <c r="BW19" s="8"/>
+      <c r="BX19" s="8"/>
+      <c r="BY19" s="8"/>
+      <c r="BZ19" s="8"/>
+      <c r="CA19" s="8"/>
+      <c r="CB19" s="8"/>
+      <c r="CC19" s="8"/>
+      <c r="CD19" s="8"/>
+      <c r="CE19" s="8"/>
+      <c r="CF19" s="8"/>
+      <c r="CG19" s="8"/>
+      <c r="CH19" s="8"/>
+      <c r="CI19" s="8"/>
+      <c r="CJ19" s="8"/>
+      <c r="CK19" s="8"/>
+      <c r="CL19" s="8"/>
+      <c r="CM19" s="8"/>
+      <c r="CN19" s="8"/>
+      <c r="CO19" s="8"/>
+      <c r="CP19" s="8"/>
+      <c r="CQ19" s="8"/>
+      <c r="CR19" s="8"/>
+      <c r="CS19" s="8"/>
+      <c r="CT19" s="8"/>
+      <c r="CU19" s="8"/>
+      <c r="CV19" s="8"/>
+      <c r="CW19" s="8"/>
+      <c r="CX19" s="8"/>
+      <c r="CY19" s="8"/>
+      <c r="CZ19" s="8"/>
+      <c r="DA19" s="8"/>
+      <c r="DB19" s="8"/>
+      <c r="DC19" s="8"/>
+      <c r="DD19" s="8"/>
+      <c r="DE19" s="8"/>
+      <c r="DF19" s="8"/>
+      <c r="DG19" s="8"/>
+      <c r="DH19" s="8"/>
+      <c r="DI19" s="8"/>
+      <c r="DJ19" s="8"/>
+      <c r="DK19" s="8"/>
+      <c r="DL19" s="8"/>
+      <c r="DM19" s="8"/>
+      <c r="DN19" s="8"/>
+      <c r="DO19" s="8"/>
+      <c r="DP19" s="8"/>
+      <c r="DQ19" s="8"/>
+      <c r="DR19" s="8"/>
+      <c r="DS19" s="8"/>
+      <c r="DT19" s="8"/>
+      <c r="DU19" s="8"/>
+      <c r="DV19" s="8"/>
+      <c r="DW19" s="8"/>
+      <c r="DX19" s="8"/>
+      <c r="DY19" s="8"/>
+      <c r="DZ19" s="8"/>
+      <c r="EA19" s="8"/>
+      <c r="EB19" s="8"/>
+      <c r="EC19" s="8"/>
+      <c r="ED19" s="8"/>
+    </row>
+    <row r="20" spans="1:134" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="3">
         <v>16</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D20" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E20" s="4" t="s">
+      <c r="D20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F20" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="G20" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="H20" s="4" t="s">
+      <c r="H20" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="I20" s="4" t="s">
+      <c r="I20" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="J20" s="5"/>
-      <c r="K20" s="5"/>
-      <c r="L20" s="5"/>
-      <c r="M20" s="5"/>
-      <c r="N20" s="5"/>
-    </row>
-    <row r="21" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="2">
+      <c r="J20" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="K20" s="4"/>
+      <c r="L20" s="4"/>
+      <c r="M20" s="4"/>
+      <c r="N20" s="4"/>
+    </row>
+    <row r="21" spans="1:134" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="1">
         <v>17</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="D21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="F21" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="G21" s="2" t="s">
+      <c r="G21" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="H21" s="2" t="s">
+      <c r="H21" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="I21" s="2" t="s">
+      <c r="I21" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="J21" s="3"/>
-      <c r="K21" s="3"/>
-      <c r="L21" s="3"/>
-      <c r="M21" s="3"/>
-      <c r="N21" s="3"/>
-    </row>
-    <row r="22" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="4">
-        <v>18</v>
-      </c>
-      <c r="B22" s="4" t="s">
+      <c r="J21" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
+    </row>
+    <row r="22" spans="1:134" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="3">
+        <v>18</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D22" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E22" s="4" t="s">
+      <c r="D22" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="F22" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="G22" s="4" t="s">
+      <c r="G22" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="H22" s="4" t="s">
+      <c r="H22" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="I22" s="4" t="s">
+      <c r="I22" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="J22" s="5"/>
-      <c r="K22" s="5"/>
-      <c r="L22" s="5"/>
-      <c r="M22" s="5"/>
-      <c r="N22" s="5"/>
-    </row>
-    <row r="23" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="2">
+      <c r="J22" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="K22" s="4"/>
+      <c r="L22" s="4"/>
+      <c r="M22" s="4"/>
+      <c r="N22" s="4"/>
+    </row>
+    <row r="23" spans="1:134" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="1">
         <v>19</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E23" s="2" t="s">
+      <c r="D23" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="F23" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="G23" s="2" t="s">
+      <c r="G23" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="H23" s="2" t="s">
+      <c r="H23" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="I23" s="2" t="s">
+      <c r="I23" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="J23" s="3"/>
-      <c r="K23" s="3"/>
-      <c r="L23" s="3"/>
-      <c r="M23" s="3"/>
-      <c r="N23" s="3"/>
-    </row>
-    <row r="24" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="4">
+      <c r="J23" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
+      <c r="N23" s="2"/>
+    </row>
+    <row r="24" spans="1:134" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="3">
         <v>20</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D24" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E24" s="4" t="s">
+      <c r="D24" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="F24" s="4" t="s">
+      <c r="F24" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="G24" s="4" t="s">
+      <c r="G24" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="H24" s="4" t="s">
+      <c r="H24" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="I24" s="4" t="s">
+      <c r="I24" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="J24" s="5"/>
-      <c r="K24" s="5"/>
-      <c r="L24" s="5"/>
-      <c r="M24" s="5"/>
-      <c r="N24" s="5"/>
-    </row>
-    <row r="25" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="2">
+      <c r="J24" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="K24" s="4"/>
+      <c r="L24" s="4"/>
+      <c r="M24" s="4"/>
+      <c r="N24" s="4"/>
+    </row>
+    <row r="25" spans="1:134" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="1">
         <v>21</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E25" s="2" t="s">
+      <c r="D25" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="F25" s="2" t="s">
+      <c r="F25" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="G25" s="2" t="s">
+      <c r="G25" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="H25" s="2" t="s">
+      <c r="H25" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="I25" s="2" t="s">
+      <c r="I25" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
-      <c r="M25" s="3"/>
-      <c r="N25" s="3"/>
-    </row>
-    <row r="26" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="4">
+      <c r="J25" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="2"/>
+      <c r="N25" s="2"/>
+    </row>
+    <row r="26" spans="1:134" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="3">
         <v>22</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D26" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E26" s="4" t="s">
+      <c r="D26" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E26" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="F26" s="4" t="s">
+      <c r="F26" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="G26" s="4" t="s">
+      <c r="G26" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="H26" s="4" t="s">
+      <c r="H26" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="I26" s="4" t="s">
+      <c r="I26" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="J26" s="5"/>
-      <c r="K26" s="5"/>
-      <c r="L26" s="5"/>
-      <c r="M26" s="5"/>
-      <c r="N26" s="5"/>
-    </row>
-    <row r="27" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="2">
+      <c r="J26" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="K26" s="4"/>
+      <c r="L26" s="4"/>
+      <c r="M26" s="4"/>
+      <c r="N26" s="4"/>
+    </row>
+    <row r="27" spans="1:134" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="1">
         <v>23</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E27" s="2" t="s">
+      <c r="D27" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E27" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="F27" s="2" t="s">
+      <c r="F27" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="G27" s="2" t="s">
+      <c r="G27" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="H27" s="2" t="s">
+      <c r="H27" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="I27" s="2" t="s">
+      <c r="I27" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="J27" s="3"/>
-      <c r="K27" s="3"/>
-      <c r="L27" s="3"/>
-      <c r="M27" s="3"/>
-      <c r="N27" s="3"/>
-    </row>
-    <row r="28" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="4">
+      <c r="J27" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
+      <c r="M27" s="2"/>
+      <c r="N27" s="2"/>
+    </row>
+    <row r="28" spans="1:134" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="3">
         <v>24</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D28" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E28" s="4" t="s">
+      <c r="D28" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E28" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="F28" s="4" t="s">
+      <c r="F28" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="G28" s="4" t="s">
+      <c r="G28" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="H28" s="4" t="s">
+      <c r="H28" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="I28" s="4" t="s">
+      <c r="I28" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="J28" s="5"/>
-      <c r="K28" s="5"/>
-      <c r="L28" s="5"/>
-      <c r="M28" s="5"/>
-      <c r="N28" s="5"/>
-    </row>
-    <row r="29" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="2">
+      <c r="J28" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="K28" s="4"/>
+      <c r="L28" s="4"/>
+      <c r="M28" s="4"/>
+      <c r="N28" s="4"/>
+    </row>
+    <row r="29" spans="1:134" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="1">
         <v>25</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E29" s="2" t="s">
+      <c r="D29" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="F29" s="2" t="s">
+      <c r="F29" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="G29" s="2" t="s">
+      <c r="G29" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="H29" s="2" t="s">
+      <c r="H29" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="I29" s="2" t="s">
+      <c r="I29" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="J29" s="3"/>
-      <c r="K29" s="3"/>
-      <c r="L29" s="3"/>
-      <c r="M29" s="3"/>
-      <c r="N29" s="3"/>
-    </row>
-    <row r="30" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="4">
+      <c r="J29" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="K29" s="2"/>
+      <c r="L29" s="2"/>
+      <c r="M29" s="2"/>
+      <c r="N29" s="2"/>
+    </row>
+    <row r="30" spans="1:134" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="3">
         <v>26</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D30" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E30" s="4" t="s">
+      <c r="D30" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E30" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="F30" s="4" t="s">
+      <c r="F30" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="G30" s="4" t="s">
+      <c r="G30" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="H30" s="4" t="s">
+      <c r="H30" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="I30" s="4" t="s">
+      <c r="I30" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="J30" s="5"/>
-      <c r="K30" s="5"/>
-      <c r="L30" s="5"/>
-      <c r="M30" s="5"/>
-      <c r="N30" s="5"/>
-    </row>
-    <row r="31" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="2">
+      <c r="J30" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="K30" s="4"/>
+      <c r="L30" s="4"/>
+      <c r="M30" s="4"/>
+      <c r="N30" s="4"/>
+    </row>
+    <row r="31" spans="1:134" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="1">
         <v>27</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E31" s="2" t="s">
+      <c r="D31" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E31" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="F31" s="2" t="s">
+      <c r="F31" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="G31" s="2" t="s">
+      <c r="G31" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="H31" s="2" t="s">
+      <c r="H31" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="I31" s="2" t="s">
+      <c r="I31" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="J31" s="3"/>
-      <c r="K31" s="3"/>
-      <c r="L31" s="3"/>
-      <c r="M31" s="3"/>
-      <c r="N31" s="3"/>
-    </row>
-    <row r="32" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="4">
+      <c r="J31" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
+      <c r="M31" s="2"/>
+      <c r="N31" s="2"/>
+    </row>
+    <row r="32" spans="1:134" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="3">
         <v>28</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="D32" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E32" s="4" t="s">
+      <c r="D32" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E32" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="F32" s="4" t="s">
+      <c r="F32" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="G32" s="4" t="s">
+      <c r="G32" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="H32" s="4" t="s">
+      <c r="H32" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="I32" s="4" t="s">
+      <c r="I32" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="J32" s="5"/>
-      <c r="K32" s="5"/>
-      <c r="L32" s="5"/>
-      <c r="M32" s="5"/>
-      <c r="N32" s="5"/>
+      <c r="J32" s="4"/>
+      <c r="K32" s="4"/>
+      <c r="L32" s="4"/>
+      <c r="M32" s="4"/>
+      <c r="N32" s="4"/>
     </row>
     <row r="33" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="2">
+      <c r="A33" s="1">
         <v>29</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="D33" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E33" s="2" t="s">
+      <c r="D33" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E33" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="F33" s="2" t="s">
+      <c r="F33" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="G33" s="2" t="s">
+      <c r="G33" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="H33" s="2" t="s">
+      <c r="H33" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="I33" s="2" t="s">
+      <c r="I33" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="J33" s="3"/>
-      <c r="K33" s="3"/>
-      <c r="L33" s="3"/>
-      <c r="M33" s="3"/>
-      <c r="N33" s="3"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="2"/>
+      <c r="L33" s="2"/>
+      <c r="M33" s="2"/>
+      <c r="N33" s="2"/>
     </row>
     <row r="34" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="4">
+      <c r="A34" s="3">
         <v>30</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C34" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="D34" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E34" s="4" t="s">
+      <c r="D34" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E34" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="F34" s="4" t="s">
+      <c r="F34" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="G34" s="4" t="s">
+      <c r="G34" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="H34" s="4" t="s">
+      <c r="H34" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="I34" s="4" t="s">
+      <c r="I34" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="J34" s="5"/>
-      <c r="K34" s="5"/>
-      <c r="L34" s="5"/>
-      <c r="M34" s="5"/>
-      <c r="N34" s="5"/>
+      <c r="J34" s="4"/>
+      <c r="K34" s="4"/>
+      <c r="L34" s="4"/>
+      <c r="M34" s="4"/>
+      <c r="N34" s="4"/>
     </row>
     <row r="35" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="2">
+      <c r="A35" s="1">
         <v>31</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="D35" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E35" s="2" t="s">
+      <c r="D35" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E35" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="F35" s="2" t="s">
+      <c r="F35" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="G35" s="2" t="s">
+      <c r="G35" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="H35" s="2" t="s">
+      <c r="H35" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="I35" s="2" t="s">
+      <c r="I35" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="J35" s="3"/>
-      <c r="K35" s="3"/>
-      <c r="L35" s="3"/>
-      <c r="M35" s="3"/>
-      <c r="N35" s="3"/>
+      <c r="J35" s="2"/>
+      <c r="K35" s="2"/>
+      <c r="L35" s="2"/>
+      <c r="M35" s="2"/>
+      <c r="N35" s="2"/>
     </row>
     <row r="36" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="4">
+      <c r="A36" s="3">
         <v>32</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="C36" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="D36" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E36" s="4" t="s">
+      <c r="D36" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E36" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="F36" s="4" t="s">
+      <c r="F36" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="G36" s="4" t="s">
+      <c r="G36" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="H36" s="4" t="s">
+      <c r="H36" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="I36" s="4" t="s">
+      <c r="I36" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="J36" s="5"/>
-      <c r="K36" s="5"/>
-      <c r="L36" s="5"/>
-      <c r="M36" s="5"/>
-      <c r="N36" s="5"/>
+      <c r="J36" s="4"/>
+      <c r="K36" s="4"/>
+      <c r="L36" s="4"/>
+      <c r="M36" s="4"/>
+      <c r="N36" s="4"/>
     </row>
     <row r="37" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="2">
+      <c r="A37" s="1">
         <v>33</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="D37" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E37" s="2" t="s">
+      <c r="D37" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E37" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="F37" s="2" t="s">
+      <c r="F37" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="G37" s="2" t="s">
+      <c r="G37" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="H37" s="2" t="s">
+      <c r="H37" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="I37" s="2" t="s">
+      <c r="I37" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="J37" s="3"/>
-      <c r="K37" s="3"/>
-      <c r="L37" s="3"/>
-      <c r="M37" s="3"/>
-      <c r="N37" s="3"/>
+      <c r="J37" s="2"/>
+      <c r="K37" s="2"/>
+      <c r="L37" s="2"/>
+      <c r="M37" s="2"/>
+      <c r="N37" s="2"/>
     </row>
     <row r="38" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="4">
+      <c r="A38" s="3">
         <v>34</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="C38" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="D38" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E38" s="4" t="s">
+      <c r="D38" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E38" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="F38" s="4" t="s">
+      <c r="F38" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="G38" s="4" t="s">
+      <c r="G38" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="H38" s="4" t="s">
+      <c r="H38" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="I38" s="4" t="s">
+      <c r="I38" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="J38" s="5"/>
-      <c r="K38" s="5"/>
-      <c r="L38" s="5"/>
-      <c r="M38" s="5"/>
-      <c r="N38" s="5"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="4"/>
+      <c r="L38" s="4"/>
+      <c r="M38" s="4"/>
+      <c r="N38" s="4"/>
     </row>
     <row r="39" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="2">
+      <c r="A39" s="1">
         <v>35</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="D39" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E39" s="2" t="s">
+      <c r="D39" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="F39" s="2" t="s">
+      <c r="F39" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="G39" s="2" t="s">
+      <c r="G39" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="H39" s="2" t="s">
+      <c r="H39" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="I39" s="2" t="s">
+      <c r="I39" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="J39" s="3"/>
-      <c r="K39" s="3"/>
-      <c r="L39" s="3"/>
-      <c r="M39" s="3"/>
-      <c r="N39" s="3"/>
+      <c r="J39" s="2"/>
+      <c r="K39" s="2"/>
+      <c r="L39" s="2"/>
+      <c r="M39" s="2"/>
+      <c r="N39" s="2"/>
     </row>
     <row r="40" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="4">
+      <c r="A40" s="3">
         <v>36</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C40" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="D40" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E40" s="4" t="s">
+      <c r="D40" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E40" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="F40" s="4" t="s">
+      <c r="F40" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="G40" s="4" t="s">
+      <c r="G40" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="H40" s="4" t="s">
+      <c r="H40" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="I40" s="4" t="s">
+      <c r="I40" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="J40" s="5"/>
-      <c r="K40" s="5"/>
-      <c r="L40" s="5"/>
-      <c r="M40" s="5"/>
-      <c r="N40" s="5"/>
+      <c r="J40" s="4"/>
+      <c r="K40" s="4"/>
+      <c r="L40" s="4"/>
+      <c r="M40" s="4"/>
+      <c r="N40" s="4"/>
     </row>
     <row r="41" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="2">
+      <c r="A41" s="1">
         <v>37</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="B41" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C41" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="D41" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E41" s="2" t="s">
+      <c r="D41" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E41" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="F41" s="2" t="s">
+      <c r="F41" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="G41" s="2" t="s">
+      <c r="G41" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="H41" s="2" t="s">
+      <c r="H41" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="I41" s="2" t="s">
+      <c r="I41" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="J41" s="3"/>
-      <c r="K41" s="3"/>
-      <c r="L41" s="3"/>
-      <c r="M41" s="3"/>
-      <c r="N41" s="3"/>
+      <c r="J41" s="2"/>
+      <c r="K41" s="2"/>
+      <c r="L41" s="2"/>
+      <c r="M41" s="2"/>
+      <c r="N41" s="2"/>
     </row>
     <row r="42" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="4">
+      <c r="A42" s="3">
         <v>38</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="B42" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="C42" s="4" t="s">
+      <c r="C42" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="D42" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E42" s="4" t="s">
+      <c r="D42" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E42" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="F42" s="4" t="s">
+      <c r="F42" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="G42" s="4" t="s">
+      <c r="G42" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="H42" s="4" t="s">
+      <c r="H42" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="I42" s="4" t="s">
+      <c r="I42" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="J42" s="5"/>
-      <c r="K42" s="5"/>
-      <c r="L42" s="5"/>
-      <c r="M42" s="5"/>
-      <c r="N42" s="5"/>
+      <c r="J42" s="4"/>
+      <c r="K42" s="4"/>
+      <c r="L42" s="4"/>
+      <c r="M42" s="4"/>
+      <c r="N42" s="4"/>
     </row>
     <row r="43" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="2">
+      <c r="A43" s="1">
         <v>39</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="B43" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C43" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="D43" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E43" s="2" t="s">
+      <c r="D43" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E43" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="F43" s="2" t="s">
+      <c r="F43" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="G43" s="2" t="s">
+      <c r="G43" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="H43" s="2" t="s">
+      <c r="H43" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="I43" s="2" t="s">
+      <c r="I43" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="J43" s="3"/>
-      <c r="K43" s="3"/>
-      <c r="L43" s="3"/>
-      <c r="M43" s="3"/>
-      <c r="N43" s="3"/>
+      <c r="J43" s="2"/>
+      <c r="K43" s="2"/>
+      <c r="L43" s="2"/>
+      <c r="M43" s="2"/>
+      <c r="N43" s="2"/>
     </row>
     <row r="44" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="4">
+      <c r="A44" s="3">
         <v>40</v>
       </c>
-      <c r="B44" s="4" t="s">
+      <c r="B44" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="C44" s="4" t="s">
+      <c r="C44" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="D44" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E44" s="4" t="s">
+      <c r="D44" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E44" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="F44" s="4" t="s">
+      <c r="F44" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="G44" s="4" t="s">
+      <c r="G44" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="H44" s="4" t="s">
+      <c r="H44" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="I44" s="4" t="s">
+      <c r="I44" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="J44" s="5"/>
-      <c r="K44" s="5"/>
-      <c r="L44" s="5"/>
-      <c r="M44" s="5"/>
-      <c r="N44" s="5"/>
+      <c r="J44" s="4"/>
+      <c r="K44" s="4"/>
+      <c r="L44" s="4"/>
+      <c r="M44" s="4"/>
+      <c r="N44" s="4"/>
     </row>
     <row r="45" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="2">
+      <c r="A45" s="1">
         <v>41</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B45" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C45" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="D45" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E45" s="2" t="s">
+      <c r="D45" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E45" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="F45" s="2" t="s">
+      <c r="F45" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="G45" s="2" t="s">
+      <c r="G45" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="H45" s="2" t="s">
+      <c r="H45" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="I45" s="2" t="s">
+      <c r="I45" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="J45" s="3"/>
-      <c r="K45" s="3"/>
-      <c r="L45" s="3"/>
-      <c r="M45" s="3"/>
-      <c r="N45" s="3"/>
+      <c r="J45" s="2"/>
+      <c r="K45" s="2"/>
+      <c r="L45" s="2"/>
+      <c r="M45" s="2"/>
+      <c r="N45" s="2"/>
     </row>
     <row r="46" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="4">
+      <c r="A46" s="3">
         <v>42</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="B46" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="C46" s="4" t="s">
+      <c r="C46" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="D46" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E46" s="4" t="s">
+      <c r="D46" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E46" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="F46" s="4" t="s">
+      <c r="F46" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="G46" s="4" t="s">
+      <c r="G46" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="H46" s="4" t="s">
+      <c r="H46" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="I46" s="4" t="s">
+      <c r="I46" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="J46" s="5"/>
-      <c r="K46" s="5"/>
-      <c r="L46" s="5"/>
-      <c r="M46" s="5"/>
-      <c r="N46" s="5"/>
+      <c r="J46" s="4"/>
+      <c r="K46" s="4"/>
+      <c r="L46" s="4"/>
+      <c r="M46" s="4"/>
+      <c r="N46" s="4"/>
     </row>
     <row r="47" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="2">
+      <c r="A47" s="1">
         <v>43</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B47" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C47" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="D47" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E47" s="2" t="s">
+      <c r="D47" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E47" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="F47" s="2" t="s">
+      <c r="F47" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="G47" s="2" t="s">
+      <c r="G47" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="H47" s="2" t="s">
+      <c r="H47" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="I47" s="2" t="s">
+      <c r="I47" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="J47" s="3"/>
-      <c r="K47" s="3"/>
-      <c r="L47" s="3"/>
-      <c r="M47" s="3"/>
-      <c r="N47" s="3"/>
+      <c r="J47" s="2"/>
+      <c r="K47" s="2"/>
+      <c r="L47" s="2"/>
+      <c r="M47" s="2"/>
+      <c r="N47" s="2"/>
     </row>
     <row r="48" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="4">
+      <c r="A48" s="3">
         <v>44</v>
       </c>
-      <c r="B48" s="4" t="s">
+      <c r="B48" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="C48" s="4" t="s">
+      <c r="C48" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="D48" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E48" s="4" t="s">
+      <c r="D48" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E48" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="F48" s="4" t="s">
+      <c r="F48" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="G48" s="4" t="s">
+      <c r="G48" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="H48" s="4" t="s">
+      <c r="H48" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="I48" s="4" t="s">
+      <c r="I48" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="J48" s="5"/>
-      <c r="K48" s="5"/>
-      <c r="L48" s="5"/>
-      <c r="M48" s="5"/>
-      <c r="N48" s="5"/>
+      <c r="J48" s="4"/>
+      <c r="K48" s="4"/>
+      <c r="L48" s="4"/>
+      <c r="M48" s="4"/>
+      <c r="N48" s="4"/>
     </row>
     <row r="49" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="2">
+      <c r="A49" s="1">
         <v>45</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="B49" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C49" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="D49" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E49" s="2" t="s">
+      <c r="D49" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E49" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="F49" s="2" t="s">
+      <c r="F49" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="G49" s="2" t="s">
+      <c r="G49" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="H49" s="2" t="s">
+      <c r="H49" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="I49" s="2" t="s">
+      <c r="I49" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="J49" s="3"/>
-      <c r="K49" s="3"/>
-      <c r="L49" s="3"/>
-      <c r="M49" s="3"/>
-      <c r="N49" s="3"/>
+      <c r="J49" s="2"/>
+      <c r="K49" s="2"/>
+      <c r="L49" s="2"/>
+      <c r="M49" s="2"/>
+      <c r="N49" s="2"/>
     </row>
     <row r="50" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="4">
+      <c r="A50" s="3">
         <v>46</v>
       </c>
-      <c r="B50" s="4" t="s">
+      <c r="B50" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="C50" s="4" t="s">
+      <c r="C50" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="D50" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E50" s="4" t="s">
+      <c r="D50" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E50" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="F50" s="4" t="s">
+      <c r="F50" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="G50" s="4" t="s">
+      <c r="G50" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="H50" s="4" t="s">
+      <c r="H50" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="I50" s="4" t="s">
+      <c r="I50" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="J50" s="5"/>
-      <c r="K50" s="5"/>
-      <c r="L50" s="5"/>
-      <c r="M50" s="5"/>
-      <c r="N50" s="5"/>
+      <c r="J50" s="4"/>
+      <c r="K50" s="4"/>
+      <c r="L50" s="4"/>
+      <c r="M50" s="4"/>
+      <c r="N50" s="4"/>
     </row>
     <row r="51" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="2">
+      <c r="A51" s="1">
         <v>47</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="B51" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="C51" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="D51" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E51" s="2" t="s">
+      <c r="D51" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E51" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="F51" s="2" t="s">
+      <c r="F51" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="G51" s="2" t="s">
+      <c r="G51" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="H51" s="2" t="s">
+      <c r="H51" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="I51" s="2" t="s">
+      <c r="I51" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="J51" s="3"/>
-      <c r="K51" s="3"/>
-      <c r="L51" s="3"/>
-      <c r="M51" s="3"/>
-      <c r="N51" s="3"/>
+      <c r="J51" s="2"/>
+      <c r="K51" s="2"/>
+      <c r="L51" s="2"/>
+      <c r="M51" s="2"/>
+      <c r="N51" s="2"/>
     </row>
     <row r="52" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="4">
+      <c r="A52" s="3">
         <v>48</v>
       </c>
-      <c r="B52" s="4" t="s">
+      <c r="B52" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="C52" s="4" t="s">
+      <c r="C52" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="D52" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E52" s="4" t="s">
+      <c r="D52" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E52" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="F52" s="4" t="s">
+      <c r="F52" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="G52" s="4" t="s">
+      <c r="G52" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="H52" s="4" t="s">
+      <c r="H52" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="I52" s="4" t="s">
+      <c r="I52" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="J52" s="5"/>
-      <c r="K52" s="5"/>
-      <c r="L52" s="5"/>
-      <c r="M52" s="5"/>
-      <c r="N52" s="5"/>
+      <c r="J52" s="4"/>
+      <c r="K52" s="4"/>
+      <c r="L52" s="4"/>
+      <c r="M52" s="4"/>
+      <c r="N52" s="4"/>
     </row>
     <row r="53" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="2">
+      <c r="A53" s="1">
         <v>49</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="B53" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="C53" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D53" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E53" s="2" t="s">
+      <c r="D53" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E53" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="F53" s="2" t="s">
+      <c r="F53" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="G53" s="2" t="s">
+      <c r="G53" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="H53" s="2" t="s">
+      <c r="H53" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="I53" s="2" t="s">
+      <c r="I53" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="J53" s="3"/>
-      <c r="K53" s="3"/>
-      <c r="L53" s="3"/>
-      <c r="M53" s="3"/>
-      <c r="N53" s="3"/>
+      <c r="J53" s="2"/>
+      <c r="K53" s="2"/>
+      <c r="L53" s="2"/>
+      <c r="M53" s="2"/>
+      <c r="N53" s="2"/>
     </row>
     <row r="54" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="4">
+      <c r="A54" s="3">
         <v>50</v>
       </c>
-      <c r="B54" s="4" t="s">
+      <c r="B54" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="C54" s="4" t="s">
+      <c r="C54" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="D54" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E54" s="4" t="s">
+      <c r="D54" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E54" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="F54" s="4" t="s">
+      <c r="F54" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="G54" s="4" t="s">
+      <c r="G54" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="H54" s="4" t="s">
+      <c r="H54" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="I54" s="4" t="s">
+      <c r="I54" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="J54" s="5"/>
-      <c r="K54" s="5"/>
-      <c r="L54" s="5"/>
-      <c r="M54" s="5"/>
-      <c r="N54" s="5"/>
+      <c r="J54" s="4"/>
+      <c r="K54" s="4"/>
+      <c r="L54" s="4"/>
+      <c r="M54" s="4"/>
+      <c r="N54" s="4"/>
     </row>
     <row r="55" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="2">
+      <c r="A55" s="1">
         <v>51</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="B55" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C55" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D55" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E55" s="2" t="s">
+      <c r="D55" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E55" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="F55" s="2" t="s">
+      <c r="F55" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="G55" s="2" t="s">
+      <c r="G55" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="H55" s="2" t="s">
+      <c r="H55" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="I55" s="2" t="s">
+      <c r="I55" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="J55" s="3"/>
-      <c r="K55" s="3"/>
-      <c r="L55" s="3"/>
-      <c r="M55" s="3"/>
-      <c r="N55" s="3"/>
+      <c r="J55" s="2"/>
+      <c r="K55" s="2"/>
+      <c r="L55" s="2"/>
+      <c r="M55" s="2"/>
+      <c r="N55" s="2"/>
     </row>
     <row r="56" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="4">
+      <c r="A56" s="3">
         <v>52</v>
       </c>
-      <c r="B56" s="4" t="s">
+      <c r="B56" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="C56" s="4" t="s">
+      <c r="C56" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="D56" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E56" s="4" t="s">
+      <c r="D56" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E56" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="F56" s="4" t="s">
+      <c r="F56" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="G56" s="4" t="s">
+      <c r="G56" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="H56" s="4" t="s">
+      <c r="H56" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="I56" s="4" t="s">
+      <c r="I56" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="J56" s="5"/>
-      <c r="K56" s="5"/>
-      <c r="L56" s="5"/>
-      <c r="M56" s="5"/>
-      <c r="N56" s="5"/>
+      <c r="J56" s="4"/>
+      <c r="K56" s="4"/>
+      <c r="L56" s="4"/>
+      <c r="M56" s="4"/>
+      <c r="N56" s="4"/>
     </row>
     <row r="57" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="2">
+      <c r="A57" s="1">
         <v>53</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="B57" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="C57" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="D57" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E57" s="2" t="s">
+      <c r="D57" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E57" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="F57" s="2" t="s">
+      <c r="F57" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="G57" s="2" t="s">
+      <c r="G57" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="H57" s="2" t="s">
+      <c r="H57" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="I57" s="2" t="s">
+      <c r="I57" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="J57" s="3"/>
-      <c r="K57" s="3"/>
-      <c r="L57" s="3"/>
-      <c r="M57" s="3"/>
-      <c r="N57" s="3"/>
+      <c r="J57" s="2"/>
+      <c r="K57" s="2"/>
+      <c r="L57" s="2"/>
+      <c r="M57" s="2"/>
+      <c r="N57" s="2"/>
     </row>
     <row r="58" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="4">
+      <c r="A58" s="3">
         <v>54</v>
       </c>
-      <c r="B58" s="4" t="s">
+      <c r="B58" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="C58" s="4" t="s">
+      <c r="C58" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="D58" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E58" s="4" t="s">
+      <c r="D58" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E58" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="F58" s="4" t="s">
+      <c r="F58" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="G58" s="4" t="s">
+      <c r="G58" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="H58" s="4" t="s">
+      <c r="H58" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="I58" s="4" t="s">
+      <c r="I58" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="J58" s="5"/>
-      <c r="K58" s="5"/>
-      <c r="L58" s="5"/>
-      <c r="M58" s="5"/>
-      <c r="N58" s="5"/>
+      <c r="J58" s="4"/>
+      <c r="K58" s="4"/>
+      <c r="L58" s="4"/>
+      <c r="M58" s="4"/>
+      <c r="N58" s="4"/>
     </row>
     <row r="59" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="2">
+      <c r="A59" s="1">
         <v>55</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="B59" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="C59" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="D59" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E59" s="2" t="s">
+      <c r="D59" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E59" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="F59" s="2" t="s">
+      <c r="F59" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="G59" s="2" t="s">
+      <c r="G59" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="H59" s="2" t="s">
+      <c r="H59" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="I59" s="2" t="s">
+      <c r="I59" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="J59" s="3"/>
-      <c r="K59" s="3"/>
-      <c r="L59" s="3"/>
-      <c r="M59" s="3"/>
-      <c r="N59" s="3"/>
+      <c r="J59" s="2"/>
+      <c r="K59" s="2"/>
+      <c r="L59" s="2"/>
+      <c r="M59" s="2"/>
+      <c r="N59" s="2"/>
     </row>
     <row r="60" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="4">
+      <c r="A60" s="3">
         <v>56</v>
       </c>
-      <c r="B60" s="4" t="s">
+      <c r="B60" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="C60" s="4" t="s">
+      <c r="C60" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="D60" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E60" s="4" t="s">
+      <c r="D60" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E60" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="F60" s="4" t="s">
+      <c r="F60" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="G60" s="4" t="s">
+      <c r="G60" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="H60" s="4" t="s">
+      <c r="H60" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="I60" s="4" t="s">
+      <c r="I60" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="J60" s="5"/>
-      <c r="K60" s="5"/>
-      <c r="L60" s="5"/>
-      <c r="M60" s="5"/>
-      <c r="N60" s="5"/>
+      <c r="J60" s="4"/>
+      <c r="K60" s="4"/>
+      <c r="L60" s="4"/>
+      <c r="M60" s="4"/>
+      <c r="N60" s="4"/>
     </row>
     <row r="61" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="2">
+      <c r="A61" s="1">
         <v>57</v>
       </c>
-      <c r="B61" s="2" t="s">
+      <c r="B61" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="C61" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="D61" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E61" s="2" t="s">
+      <c r="D61" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E61" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="F61" s="2" t="s">
+      <c r="F61" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="G61" s="2" t="s">
+      <c r="G61" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="H61" s="2" t="s">
+      <c r="H61" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="I61" s="2" t="s">
+      <c r="I61" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="J61" s="3"/>
-      <c r="K61" s="3"/>
-      <c r="L61" s="3"/>
-      <c r="M61" s="3"/>
-      <c r="N61" s="3"/>
+      <c r="J61" s="2"/>
+      <c r="K61" s="2"/>
+      <c r="L61" s="2"/>
+      <c r="M61" s="2"/>
+      <c r="N61" s="2"/>
     </row>
     <row r="62" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="4">
+      <c r="A62" s="3">
         <v>58</v>
       </c>
-      <c r="B62" s="4" t="s">
+      <c r="B62" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="C62" s="4" t="s">
+      <c r="C62" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="D62" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E62" s="4" t="s">
+      <c r="D62" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E62" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="F62" s="4" t="s">
+      <c r="F62" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="G62" s="4" t="s">
+      <c r="G62" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="H62" s="4" t="s">
+      <c r="H62" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="I62" s="4" t="s">
+      <c r="I62" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="J62" s="5"/>
-      <c r="K62" s="5"/>
-      <c r="L62" s="5"/>
-      <c r="M62" s="5"/>
-      <c r="N62" s="5"/>
+      <c r="J62" s="4"/>
+      <c r="K62" s="4"/>
+      <c r="L62" s="4"/>
+      <c r="M62" s="4"/>
+      <c r="N62" s="4"/>
     </row>
     <row r="63" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="2">
+      <c r="A63" s="1">
         <v>59</v>
       </c>
-      <c r="B63" s="2" t="s">
+      <c r="B63" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="C63" s="2" t="s">
+      <c r="C63" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="D63" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E63" s="2" t="s">
+      <c r="D63" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E63" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="F63" s="2" t="s">
+      <c r="F63" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="G63" s="2" t="s">
+      <c r="G63" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="H63" s="2" t="s">
+      <c r="H63" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="I63" s="2" t="s">
+      <c r="I63" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="J63" s="3"/>
-      <c r="K63" s="3"/>
-      <c r="L63" s="3"/>
-      <c r="M63" s="3"/>
-      <c r="N63" s="3"/>
+      <c r="J63" s="2"/>
+      <c r="K63" s="2"/>
+      <c r="L63" s="2"/>
+      <c r="M63" s="2"/>
+      <c r="N63" s="2"/>
     </row>
     <row r="64" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="4">
+      <c r="A64" s="3">
         <v>60</v>
       </c>
-      <c r="B64" s="4" t="s">
+      <c r="B64" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="C64" s="4" t="s">
+      <c r="C64" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="D64" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E64" s="4" t="s">
+      <c r="D64" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E64" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="F64" s="4" t="s">
+      <c r="F64" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="G64" s="4" t="s">
+      <c r="G64" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="H64" s="4" t="s">
+      <c r="H64" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="I64" s="4" t="s">
+      <c r="I64" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="J64" s="5"/>
-      <c r="K64" s="5"/>
-      <c r="L64" s="5"/>
-      <c r="M64" s="5"/>
-      <c r="N64" s="5"/>
+      <c r="J64" s="4"/>
+      <c r="K64" s="4"/>
+      <c r="L64" s="4"/>
+      <c r="M64" s="4"/>
+      <c r="N64" s="4"/>
     </row>
     <row r="65" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="2">
+      <c r="A65" s="1">
         <v>61</v>
       </c>
-      <c r="B65" s="2" t="s">
+      <c r="B65" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="C65" s="2" t="s">
+      <c r="C65" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="D65" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E65" s="2" t="s">
+      <c r="D65" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E65" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="F65" s="2" t="s">
+      <c r="F65" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="G65" s="2" t="s">
+      <c r="G65" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="H65" s="2" t="s">
+      <c r="H65" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="I65" s="2" t="s">
+      <c r="I65" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="J65" s="3"/>
-      <c r="K65" s="3"/>
-      <c r="L65" s="3"/>
-      <c r="M65" s="3"/>
-      <c r="N65" s="3"/>
+      <c r="J65" s="2"/>
+      <c r="K65" s="2"/>
+      <c r="L65" s="2"/>
+      <c r="M65" s="2"/>
+      <c r="N65" s="2"/>
     </row>
     <row r="66" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="4">
+      <c r="A66" s="3">
         <v>62</v>
       </c>
-      <c r="B66" s="4" t="s">
+      <c r="B66" s="3" t="s">
         <v>384</v>
       </c>
-      <c r="C66" s="4" t="s">
+      <c r="C66" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="D66" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E66" s="4" t="s">
+      <c r="D66" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E66" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="F66" s="4" t="s">
+      <c r="F66" s="3" t="s">
         <v>386</v>
       </c>
-      <c r="G66" s="4" t="s">
+      <c r="G66" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="H66" s="4" t="s">
+      <c r="H66" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="I66" s="4" t="s">
+      <c r="I66" s="3" t="s">
         <v>389</v>
       </c>
-      <c r="J66" s="5"/>
-      <c r="K66" s="5"/>
-      <c r="L66" s="5"/>
-      <c r="M66" s="5"/>
-      <c r="N66" s="5"/>
+      <c r="J66" s="4"/>
+      <c r="K66" s="4"/>
+      <c r="L66" s="4"/>
+      <c r="M66" s="4"/>
+      <c r="N66" s="4"/>
     </row>
     <row r="67" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="2">
+      <c r="A67" s="1">
         <v>63</v>
       </c>
-      <c r="B67" s="2" t="s">
+      <c r="B67" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="C67" s="2" t="s">
+      <c r="C67" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="D67" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E67" s="2" t="s">
+      <c r="D67" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E67" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="F67" s="2" t="s">
+      <c r="F67" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="G67" s="2" t="s">
+      <c r="G67" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="H67" s="2" t="s">
+      <c r="H67" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="I67" s="2" t="s">
+      <c r="I67" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="J67" s="3"/>
-      <c r="K67" s="3"/>
-      <c r="L67" s="3"/>
-      <c r="M67" s="3"/>
-      <c r="N67" s="3"/>
+      <c r="J67" s="2"/>
+      <c r="K67" s="2"/>
+      <c r="L67" s="2"/>
+      <c r="M67" s="2"/>
+      <c r="N67" s="2"/>
     </row>
     <row r="68" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="4">
+      <c r="A68" s="3">
         <v>64</v>
       </c>
-      <c r="B68" s="4" t="s">
+      <c r="B68" s="3" t="s">
         <v>397</v>
       </c>
-      <c r="C68" s="4" t="s">
+      <c r="C68" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="D68" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E68" s="4" t="s">
+      <c r="D68" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E68" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="F68" s="4" t="s">
+      <c r="F68" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="G68" s="4" t="s">
+      <c r="G68" s="3" t="s">
         <v>400</v>
       </c>
-      <c r="H68" s="4" t="s">
+      <c r="H68" s="3" t="s">
         <v>401</v>
       </c>
-      <c r="I68" s="4" t="s">
+      <c r="I68" s="3" t="s">
         <v>402</v>
       </c>
-      <c r="J68" s="5"/>
-      <c r="K68" s="5"/>
-      <c r="L68" s="5"/>
-      <c r="M68" s="5"/>
-      <c r="N68" s="5"/>
+      <c r="J68" s="4"/>
+      <c r="K68" s="4"/>
+      <c r="L68" s="4"/>
+      <c r="M68" s="4"/>
+      <c r="N68" s="4"/>
     </row>
     <row r="69" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="2">
+      <c r="A69" s="1">
         <v>65</v>
       </c>
-      <c r="B69" s="2" t="s">
+      <c r="B69" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="C69" s="2" t="s">
+      <c r="C69" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="D69" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E69" s="2" t="s">
+      <c r="D69" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E69" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="F69" s="2" t="s">
+      <c r="F69" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="G69" s="2" t="s">
+      <c r="G69" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="H69" s="2" t="s">
+      <c r="H69" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="I69" s="2" t="s">
+      <c r="I69" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="J69" s="3"/>
-      <c r="K69" s="3"/>
-      <c r="L69" s="3"/>
-      <c r="M69" s="3"/>
-      <c r="N69" s="3"/>
+      <c r="J69" s="2"/>
+      <c r="K69" s="2"/>
+      <c r="L69" s="2"/>
+      <c r="M69" s="2"/>
+      <c r="N69" s="2"/>
     </row>
     <row r="70" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="4">
+      <c r="A70" s="3">
         <v>66</v>
       </c>
-      <c r="B70" s="4" t="s">
+      <c r="B70" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="C70" s="4" t="s">
+      <c r="C70" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="D70" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E70" s="4" t="s">
+      <c r="D70" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E70" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="F70" s="4" t="s">
+      <c r="F70" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="G70" s="4" t="s">
+      <c r="G70" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="H70" s="4" t="s">
+      <c r="H70" s="3" t="s">
         <v>395</v>
       </c>
-      <c r="I70" s="4" t="s">
+      <c r="I70" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="J70" s="5"/>
-      <c r="K70" s="5"/>
-      <c r="L70" s="5"/>
-      <c r="M70" s="5"/>
-      <c r="N70" s="5"/>
+      <c r="J70" s="4"/>
+      <c r="K70" s="4"/>
+      <c r="L70" s="4"/>
+      <c r="M70" s="4"/>
+      <c r="N70" s="4"/>
     </row>
     <row r="71" spans="1:14" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="2">
+      <c r="A71" s="1">
         <v>67</v>
       </c>
-      <c r="B71" s="2" t="s">
+      <c r="B71" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="C71" s="2" t="s">
+      <c r="C71" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="D71" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E71" s="2" t="s">
+      <c r="D71" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E71" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="F71" s="2" t="s">
+      <c r="F71" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="G71" s="2" t="s">
+      <c r="G71" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="H71" s="2" t="s">
+      <c r="H71" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="I71" s="2" t="s">
+      <c r="I71" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="J71" s="3"/>
-      <c r="K71" s="3"/>
-      <c r="L71" s="3"/>
-      <c r="M71" s="3"/>
-      <c r="N71" s="3"/>
+      <c r="J71" s="2"/>
+      <c r="K71" s="2"/>
+      <c r="L71" s="2"/>
+      <c r="M71" s="2"/>
+      <c r="N71" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:N71" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -4175,5 +6566,6 @@
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>